--- a/modelo_receitas_atualizado.xlsx
+++ b/modelo_receitas_atualizado.xlsx
@@ -1,218 +1,897 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\walte\Desktop\MilkShakeMix_Cardapio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11F9490C-F128-4AA1-94F1-D6B40081FF01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A939CE12-D99D-405D-9928-F1ACB136F930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Receitas" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="59">
-  <si>
-    <t>Categoria</t>
-  </si>
-  <si>
-    <t>Produto</t>
-  </si>
-  <si>
-    <t>Tamanho</t>
-  </si>
-  <si>
-    <t>Ingredientes</t>
-  </si>
-  <si>
-    <t>Modo de Preparo</t>
-  </si>
-  <si>
-    <t>Observações</t>
-  </si>
-  <si>
-    <t>Imagem</t>
-  </si>
-  <si>
-    <t>MilkShakes Tradicionais</t>
-  </si>
-  <si>
-    <t>MilkShakes Especiais</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1217" uniqueCount="288">
+  <si>
+    <t>LINHA</t>
+  </si>
+  <si>
+    <t>PRODUTO</t>
+  </si>
+  <si>
+    <t>TAMANHO</t>
+  </si>
+  <si>
+    <t>INGREDIENTES</t>
+  </si>
+  <si>
+    <t>MODO DE PREPARO</t>
+  </si>
+  <si>
+    <t>OBSERVAÇÕES</t>
+  </si>
+  <si>
+    <t>IMAGEM</t>
+  </si>
+  <si>
+    <t>Milkshakes Tradicionais</t>
+  </si>
+  <si>
+    <t>Abacaxi</t>
+  </si>
+  <si>
+    <t>250ml</t>
+  </si>
+  <si>
+    <t>Cobertura de abacaxi c/ pedaços; Sorvete de baunilha; Cobertura de abacaxi Marvi</t>
+  </si>
+  <si>
+    <t>Decore o copo com cobertura de abacaxi Marvi. Adicione a cobertura c/ pedaços e o sorvete de baunilha. Misture no batedor até homogeneizar. Opcional: finalize com 1/2 concha de cobertura de abacaxi.</t>
+  </si>
+  <si>
+    <t>abacaxi.jpg</t>
+  </si>
+  <si>
+    <t>400ml</t>
+  </si>
+  <si>
+    <t>500ml</t>
+  </si>
+  <si>
+    <t>700ml</t>
+  </si>
+  <si>
+    <t>Abacaxi ao Vinho</t>
+  </si>
+  <si>
+    <t>Preparado de abacaxi ao vinho; Sorvete de baunilha</t>
+  </si>
+  <si>
+    <t>Coloque o preparado de abacaxi ao vinho (medida da tabela) e o sorvete de baunilha. Misture no batedor até homogeneizar.</t>
+  </si>
+  <si>
+    <t>abacaxi_vinho.jpg</t>
+  </si>
+  <si>
+    <t>Abacaxi com Hortelã</t>
+  </si>
+  <si>
+    <t>Cobertura de abacaxi c/ pedaços; Pó de abacaxi com hortelã; Sorvete de baunilha</t>
+  </si>
+  <si>
+    <t>Decore o copo com cobertura de abacaxi Marvi. Adicione a cobertura c/ pedaços, o pó de abacaxi com hortelã (medida da tabela) e o sorvete. Misture no batedor.</t>
+  </si>
+  <si>
+    <t>abacaxi_hortela.jpg</t>
+  </si>
+  <si>
+    <t>Açaí</t>
+  </si>
+  <si>
+    <t>Algodão Doce</t>
+  </si>
+  <si>
+    <t>Pó blue ice; Sorvete de baunilha; Leite; Cobertura de groselha azul Marvi</t>
+  </si>
+  <si>
+    <t>Decore o copo com cobertura de groselha azul Marvi. Adicione leite até a marcação, o pó blue ice (medida da tabela) e o sorvete. Misture no batedor.</t>
+  </si>
+  <si>
+    <t>algodao_doce.jpg</t>
+  </si>
+  <si>
+    <t>Ameixa</t>
+  </si>
+  <si>
+    <t>Cobertura de ameixa; Sorvete de baunilha</t>
+  </si>
+  <si>
+    <t>Adicione a cobertura de ameixa (medida da tabela) e o sorvete de baunilha. Misture no batedor.</t>
+  </si>
+  <si>
+    <t>ameixa.jpg</t>
+  </si>
+  <si>
+    <t>Amendoim</t>
+  </si>
+  <si>
+    <t>Pasta de amendoim; Amendoim torrado granulado; Sorvete de baunilha; Leite</t>
+  </si>
+  <si>
+    <t>Adicione leite até a marcação; coloque a pasta de amendoim e misture no batedor; acrescente o sorvete e o amendoim torrado. Misture levemente com o batedor desligado, fazendo movimentos circulares para manter a crocância. Opcional: finalize com 25% da medida D de amendoim torrado.</t>
+  </si>
+  <si>
+    <t>amendoim.jpg</t>
+  </si>
+  <si>
+    <t>Amora</t>
+  </si>
+  <si>
+    <t>Cobertura de amora; Sorvete de baunilha</t>
+  </si>
+  <si>
+    <t>Adicione a cobertura de amora (medida da tabela) e o sorvete de baunilha. Misture no batedor.</t>
+  </si>
+  <si>
+    <t>amora.jpg</t>
+  </si>
+  <si>
+    <t>Banana</t>
+  </si>
+  <si>
+    <t>Pó de banana; Sorvete de baunilha; Leite</t>
+  </si>
+  <si>
+    <t>Adicione leite até a marcação; coloque o pó de banana (medida da tabela) e o sorvete. Misture no batedor.</t>
+  </si>
+  <si>
+    <t>banana.jpg</t>
+  </si>
+  <si>
+    <t>Banana com Canela</t>
+  </si>
+  <si>
+    <t>Pó de banana com canela; Sorvete de baunilha; Leite; Cobertura de caramelo Marvi</t>
+  </si>
+  <si>
+    <t>Decore o copo com cobertura de caramelo Marvi. Adicione leite até a marcação; coloque o pó de banana com canela (medida da tabela) e o sorvete. Misture no batedor.</t>
+  </si>
+  <si>
+    <t>banana_canela.jpg</t>
+  </si>
+  <si>
+    <t>Beijinho</t>
+  </si>
+  <si>
+    <t>Pó de beijinho (medida A); Coco ralado (medida D); Sorvete de baunilha; Leite; Cobertura de leite condensado Marvi</t>
+  </si>
+  <si>
+    <t>Decore o copo com cobertura de leite condensado Marvi. Adicione leite até a marcação; coloque o pó de beijinho (A) e misture no batedor; acrescente o sorvete e o coco ralado (D). Misture levemente com o batedor desligado. Opcional: finalize com 25% da medida D de coco.</t>
+  </si>
+  <si>
+    <t>beijinho.jpg</t>
+  </si>
+  <si>
+    <t>Brigadeiro</t>
+  </si>
+  <si>
+    <t>Pó de leite condensado (50% medida A); Granulado macio (medida D); Sorvete de chocolate; Leite; Cobertura de brigadeiro Marvi</t>
+  </si>
+  <si>
+    <t>Decore o copo com cobertura de brigadeiro Marvi. Adicione leite até a marcação; coloque o pó de leite condensado, o granulado e o sorvete de chocolate. Misture no batedor. Opcional: finalize com granulado (25% da medida D).</t>
+  </si>
+  <si>
+    <t>brigadeiro.jpg</t>
+  </si>
+  <si>
+    <t>Capuccino</t>
+  </si>
+  <si>
+    <t>Capuccino (2 medidas A); Sorvete de baunilha; Leite; Cobertura de caramelo Marvi</t>
+  </si>
+  <si>
+    <t>Decore o copo com cobertura de caramelo Marvi. Adicione leite até a marcação; coloque o capuccino (2 medidas A) e o sorvete de baunilha. Misture no batedor.</t>
+  </si>
+  <si>
+    <t>capuccino.jpg</t>
+  </si>
+  <si>
+    <t>Cereja</t>
+  </si>
+  <si>
+    <t>Pó de cereja (medida A); Sorvete de baunilha; Leite; Cobertura de cereja Marvi</t>
+  </si>
+  <si>
+    <t>Decore o copo com cobertura de cereja Marvi. Adicione leite até a marcação; coloque o pó de cereja e o sorvete de baunilha. Misture no batedor.</t>
+  </si>
+  <si>
+    <t>cereja.jpg</t>
+  </si>
+  <si>
+    <t>Charge</t>
+  </si>
+  <si>
+    <t>Pasta integral de amendoim; Amendoim torrado granulado (medida D); Sorvete misto; Leite; Cobertura de caramelo Marvi</t>
+  </si>
+  <si>
+    <t>Decore o copo com cobertura de caramelo Marvi. Adicione leite até a marcação; coloque a pasta de amendoim e misture no batedor; acrescente o sorvete e o amendoim torrado. Misture levemente com o batedor desligado. Opcional: finalize com 25% da medida D de amendoim torrado.</t>
+  </si>
+  <si>
+    <t>charge.jpg</t>
+  </si>
+  <si>
+    <t>Chiclete</t>
+  </si>
+  <si>
+    <t>250ml / 400ml / 500ml / 700ml</t>
+  </si>
+  <si>
+    <t>PENDENTE TRANSCRIÇÃO A PARTIR DA FOTO</t>
+  </si>
+  <si>
+    <t>chiclete.jpg</t>
+  </si>
+  <si>
+    <t>Chocolate</t>
+  </si>
+  <si>
+    <t>chocolate.jpg</t>
+  </si>
+  <si>
+    <t>Coco</t>
+  </si>
+  <si>
+    <t>coco.jpg</t>
+  </si>
+  <si>
+    <t>Creme</t>
+  </si>
+  <si>
+    <t>creme.jpg</t>
+  </si>
+  <si>
+    <t>Flocos</t>
+  </si>
+  <si>
+    <t>flocos.jpg</t>
+  </si>
+  <si>
+    <t>Menta</t>
+  </si>
+  <si>
+    <t>menta.jpg</t>
+  </si>
+  <si>
+    <t>Napolitano</t>
+  </si>
+  <si>
+    <t>napolitano.jpg</t>
+  </si>
+  <si>
+    <t>Uva</t>
+  </si>
+  <si>
+    <t>uva.jpg</t>
+  </si>
+  <si>
+    <t>Milk Shakes Especiais</t>
+  </si>
+  <si>
+    <t>Sonho de Valsa</t>
+  </si>
+  <si>
+    <t>Recheio Variegato Bombom Vabene; Sorvete de baunilha; Leite; Bombom Sonho de Valsa; Castanha de caju crua</t>
+  </si>
+  <si>
+    <t>Decore o copo com o recheio Variegato Bombom Vabene (medidas por tamanho). Coloque o leite até a marcação, acrescente o sorvete e misture no batedor. Complete com mais sorvete e misture novamente. Finalize com 25% da medida D de castanha de caju e 1 bombom Sonho de Valsa cortado ao meio.</t>
+  </si>
+  <si>
+    <t>sonho_de_valsa.jpg</t>
+  </si>
+  <si>
+    <t>Ouro Branco</t>
+  </si>
+  <si>
+    <t>Recheio Variegato Bombom Vabene; Sorvete misto; Leite; Bombom Ouro Branco</t>
+  </si>
+  <si>
+    <t>Decore o copo com o recheio Variegato Bombom Vabene (medidas por tamanho). Coloque o leite até a marcação, acrescente o sorvete e misture no batedor. Complete e misture novamente. Finalize com 1 bombom Ouro Branco cortado ao meio.</t>
+  </si>
+  <si>
+    <t>ouro_branco.jpg</t>
+  </si>
+  <si>
+    <t>Laka</t>
+  </si>
+  <si>
+    <t>Recheio Ganache Chocolate Branco Vabene; Sorvete de baunilha; Leite</t>
+  </si>
+  <si>
+    <t>Adicione leite até a marcação; acrescente o recheio ganache chocolate branco e o sorvete; bata até homogeneizar; finalize com um fio de ganache.</t>
+  </si>
+  <si>
+    <t>laka.jpg</t>
+  </si>
+  <si>
+    <t>Laka Oreo</t>
+  </si>
+  <si>
+    <t>Recheio Ganache Chocolate Branco Vabene; Sorvete de baunilha; Leite; Mini Oreo</t>
+  </si>
+  <si>
+    <t>Adicione leite até a marcação; acrescente o recheio ganache chocolate branco, o sorvete e mini Oreo triturado; bata até homogeneizar; finalize com Oreo por cima.</t>
+  </si>
+  <si>
+    <t>laka_oreo.jpg</t>
+  </si>
+  <si>
+    <t>Brownie</t>
+  </si>
+  <si>
+    <t>Recheio Brownie; Sorvete de chocolate; Leite</t>
+  </si>
+  <si>
+    <t>Adicione leite até a marcação; acrescente o recheio brownie e o sorvete de chocolate; bata; finalize com 1/2 concha de recheio brownie.</t>
+  </si>
+  <si>
+    <t>brownie.jpg</t>
+  </si>
+  <si>
+    <t>Pão de Mel</t>
+  </si>
+  <si>
+    <t>Recheio Pão de Mel; Sorvete misto; Leite</t>
+  </si>
+  <si>
+    <t>Adicione leite até a marcação; acrescente o recheio pão de mel e o sorvete misto; bata; finalize com um fio do recheio.</t>
+  </si>
+  <si>
+    <t>pao_de_mel.jpg</t>
+  </si>
+  <si>
+    <t>Diamante Negro</t>
+  </si>
+  <si>
+    <t>A preencher depois</t>
+  </si>
+  <si>
+    <t>diamante_negro.jpg</t>
+  </si>
+  <si>
+    <t>Ferrero Rocher</t>
+  </si>
+  <si>
+    <t>Frutas Vermelhas</t>
+  </si>
+  <si>
+    <t>Leite Ninho</t>
+  </si>
+  <si>
+    <t>Nutella</t>
+  </si>
+  <si>
+    <t>Ovo Ninho</t>
+  </si>
+  <si>
+    <t>Proibido com Nutella</t>
+  </si>
+  <si>
+    <t>Torta de Limão</t>
+  </si>
+  <si>
+    <t>Cupuaçu</t>
+  </si>
+  <si>
+    <t>Floresta Negra</t>
+  </si>
+  <si>
+    <t>Cookie</t>
+  </si>
+  <si>
+    <t>Mix Chocolate</t>
+  </si>
+  <si>
+    <t>Mix Suflair</t>
+  </si>
+  <si>
+    <t>240ml</t>
+  </si>
+  <si>
+    <t>Sorvete de baunilha; Cobertura de chocolate; Suflair em pedaços</t>
+  </si>
+  <si>
+    <t>Monte em camadas de sorvete e Suflair; finalize com cobertura de chocolate.</t>
+  </si>
+  <si>
+    <t>mix_suflair.jpg</t>
+  </si>
+  <si>
+    <t>Mix KitKat</t>
+  </si>
+  <si>
+    <t>Sorvete de baunilha; Cobertura de chocolate; KitKat picado</t>
+  </si>
+  <si>
+    <t>Monte em camadas de sorvete e KitKat; finalize com cobertura de chocolate.</t>
+  </si>
+  <si>
+    <t>mix_kitkat.jpg</t>
+  </si>
+  <si>
+    <t>Mix Ovomaltine</t>
+  </si>
+  <si>
+    <t>Sorvete de baunilha; Cobertura de chocolate; Ovomaltine</t>
+  </si>
+  <si>
+    <t>Monte em camadas de sorvete e Ovomaltine; finalize com cobertura de chocolate.</t>
+  </si>
+  <si>
+    <t>mix_ovomaltine.jpg</t>
+  </si>
+  <si>
+    <t>Mix Kids</t>
+  </si>
+  <si>
+    <t>Mix Fini</t>
+  </si>
+  <si>
+    <t>Sorvete; Cobertura de morango; Balas Fini</t>
+  </si>
+  <si>
+    <t>Metade do pote com sorvete; 1 concha de cobertura; complete com sorvete; finalize com 1/2 concha e balas Fini por cima.</t>
+  </si>
+  <si>
+    <t>mix_fini.jpg</t>
+  </si>
+  <si>
+    <t>Mix Merengue</t>
+  </si>
+  <si>
+    <t>Sorvete; Cobertura de morango; Mini suspiro</t>
+  </si>
+  <si>
+    <t>Metade do pote com sorvete; 1 concha de cobertura + mini suspiro picado; complete com sorvete; finalize com 1/2 concha e mini suspiro por cima.</t>
+  </si>
+  <si>
+    <t>mix_merengue.jpg</t>
+  </si>
+  <si>
+    <t>Mix Algodão Doce</t>
+  </si>
+  <si>
+    <t>mix_algodao_doce.jpg</t>
+  </si>
+  <si>
+    <t>Mix Brigadeiro</t>
+  </si>
+  <si>
+    <t>mix_brigadeiro.jpg</t>
+  </si>
+  <si>
+    <t>Mix Confeti</t>
+  </si>
+  <si>
+    <t>mix_confeti.jpg</t>
+  </si>
+  <si>
+    <t>Mix Fruta</t>
+  </si>
+  <si>
+    <t>Mix Fruta Morango</t>
+  </si>
+  <si>
+    <t>Sorvete de baunilha; Cobertura de morango</t>
+  </si>
+  <si>
+    <t>Coloque sorvete no pote fazendo bico; finalize com 1 concha de cobertura de morango em volta do bico.</t>
+  </si>
+  <si>
+    <t>mix_fruta_morango.jpg</t>
+  </si>
+  <si>
+    <t>Mix Fruta Maracujá</t>
+  </si>
+  <si>
+    <t>Sorvete de baunilha; Cobertura de maracujá</t>
+  </si>
+  <si>
+    <t>Coloque sorvete no pote fazendo bico; finalize com 1 concha de cobertura de maracujá em volta do bico.</t>
+  </si>
+  <si>
+    <t>mix_fruta_maracujá.jpg</t>
+  </si>
+  <si>
+    <t>Mix Fruta Framboesa</t>
+  </si>
+  <si>
+    <t>Sorvete de baunilha; Cobertura de framboesa</t>
+  </si>
+  <si>
+    <t>Coloque sorvete no pote fazendo bico; finalize com 1 concha de cobertura de framboesa em volta do bico.</t>
+  </si>
+  <si>
+    <t>mix_fruta_framboesa.jpg</t>
+  </si>
+  <si>
+    <t>Mix Fruta Amora</t>
+  </si>
+  <si>
+    <t>Sorvete de baunilha; Cobertura de amora</t>
+  </si>
+  <si>
+    <t>Coloque sorvete no pote fazendo bico; finalize com 1 concha de cobertura de amora em volta do bico.</t>
+  </si>
+  <si>
+    <t>mix_fruta_amora.jpg</t>
+  </si>
+  <si>
+    <t>Mix Fruta Abacaxi</t>
+  </si>
+  <si>
+    <t>Sorvete de baunilha; Cobertura de abacaxi</t>
+  </si>
+  <si>
+    <t>Coloque sorvete no pote fazendo bico; finalize com 1 concha de cobertura de abacaxi em volta do bico.</t>
+  </si>
+  <si>
+    <t>mix_fruta_abacaxi.jpg</t>
   </si>
   <si>
     <t>Mix Twist</t>
   </si>
   <si>
-    <t>Mix Frutas</t>
-  </si>
-  <si>
-    <t>Mix Chocolate</t>
-  </si>
-  <si>
-    <t>Sundae</t>
+    <t>Mix Twist Banana c/ Farinha Láctea e Doce de Leite</t>
+  </si>
+  <si>
+    <t>320ml / 330ml</t>
+  </si>
+  <si>
+    <t>Sorvete de baunilha; Banana em pedaços; Farinha láctea (medida D); Cobertura de doce de leite</t>
+  </si>
+  <si>
+    <t>Coloque um pouco de sorvete; adicione banana, 1 bombada de doce de leite e 1 medida D de farinha láctea; misture levemente; repita até encher; finalize com farinha láctea (medida D) e banana por cima.</t>
+  </si>
+  <si>
+    <t>mix_twist_banana_farlactea.jpg</t>
+  </si>
+  <si>
+    <t>Mix Twist Confeti Trufado</t>
+  </si>
+  <si>
+    <t>Sorvete de baunilha; Disquete (confeti) medida D; Creme trufado</t>
+  </si>
+  <si>
+    <t>Coloque um pouco de sorvete; 1 medida D de confeti; 1 bombada de creme trufado; misture levemente; repita até encher; finalize com confeti (medida D).</t>
+  </si>
+  <si>
+    <t>mix_twist_confeti_trufado.jpg</t>
+  </si>
+  <si>
+    <t>Mix Twist Maracujá Trufado</t>
+  </si>
+  <si>
+    <t>Sorvete de baunilha; Cobertura de maracujá; Creme trufado</t>
+  </si>
+  <si>
+    <t>Coloque um pouco de sorvete; 1 concha de cobertura de maracujá; 1 bombada de creme trufado; misture levemente; repita até encher; finalize com 1/2 concha de maracujá.</t>
+  </si>
+  <si>
+    <t>mix_twist_maracuja_trufado.jpg</t>
+  </si>
+  <si>
+    <t>Mix Twist Morango Trufado</t>
+  </si>
+  <si>
+    <t>Sorvete de baunilha; Cobertura de morango; Creme trufado</t>
+  </si>
+  <si>
+    <t>Coloque um pouco de sorvete; 1 concha de cobertura de morango; 1 bombada de creme trufado; misture levemente; repita até encher; finalize com 1/2 concha de morango.</t>
+  </si>
+  <si>
+    <t>mix_twist_morango_trufado.jpg</t>
+  </si>
+  <si>
+    <t>Mix Twist Morango e Sucrilhos</t>
+  </si>
+  <si>
+    <t>Sorvete de baunilha; Cobertura de morango; Sucrilhos (medida D)</t>
+  </si>
+  <si>
+    <t>Coloque um pouco de sorvete; 1 concha de cobertura de morango; 1 medida D de sucrilhos; misture levemente; repita até encher; finalize com sucrilhos por cima (medida D).</t>
+  </si>
+  <si>
+    <t>mix_twist_morango_sucrilhos.jpg</t>
+  </si>
+  <si>
+    <t>Mix Twist Sucrilhos Trufado</t>
+  </si>
+  <si>
+    <t>Sorvete de baunilha; Creme trufado; Sucrilhos (medida D)</t>
+  </si>
+  <si>
+    <t>Coloque um pouco de sorvete; 1 bombada de creme trufado; 1 medida D de sucrilhos; misture levemente; repita até encher; finalize com sucrilhos (medida D).</t>
+  </si>
+  <si>
+    <t>mix_twist_sucrilhos_trufado.jpg</t>
+  </si>
+  <si>
+    <t>Mix Twist Negresco e Doce de Leite</t>
+  </si>
+  <si>
+    <t>Sorvete de baunilha; Negresco (medida D); Cobertura de doce de leite</t>
+  </si>
+  <si>
+    <t>Coloque um pouco de sorvete; 1 bombada de doce de leite; 1 medida D de negresco; misture levemente; repita até encher; finalize com negresco (medida D).</t>
+  </si>
+  <si>
+    <t>mix_twist_negresco_doceleite.jpg</t>
+  </si>
+  <si>
+    <t>Mix Twist Negresco Trufado</t>
+  </si>
+  <si>
+    <t>Sorvete de baunilha; Negresco (medida D); Creme trufado</t>
+  </si>
+  <si>
+    <t>Coloque um pouco de sorvete; 1 bombada de creme trufado; 1 medida D de negresco; misture levemente; repita; finalize com negresco (medida D).</t>
+  </si>
+  <si>
+    <t>mix_twist_negresco_trufado.jpg</t>
+  </si>
+  <si>
+    <t>Mix Twist Ovomaltine Trufado</t>
+  </si>
+  <si>
+    <t>Sorvete de baunilha; Ovomaltine (medida D); Creme trufado</t>
+  </si>
+  <si>
+    <t>Coloque um pouco de sorvete; 1 medida D de Ovomaltine; 1 bombada de creme trufado; misture levemente; repita; finalize com Ovomaltine (medida D).</t>
+  </si>
+  <si>
+    <t>mix_twist_ovomaltine_trufado.jpg</t>
+  </si>
+  <si>
+    <t>Mix Twist Ninho Trufado</t>
+  </si>
+  <si>
+    <t>Sorvete de baunilha; Leite Ninho (medida D); Creme trufado (1/2 bombada)</t>
+  </si>
+  <si>
+    <t>Coloque um pouco de sorvete; 1 medida D de leite ninho; 1/2 bombada de creme trufado; misture levemente; repita; finalize com leite ninho (medida D).</t>
+  </si>
+  <si>
+    <t>mix_twist_ninho_trufado.jpg</t>
+  </si>
+  <si>
+    <t>Mix Twist Laka Oreo</t>
+  </si>
+  <si>
+    <t>Recheio Ganache Chocolate Branco Vabene; Sorvete de baunilha; Mini Oreo</t>
+  </si>
+  <si>
+    <t>Coloque um pouco de sorvete; 1 concha de ganache branco; 2 mini Oreo trituradas; misture levemente; complete com sorvete; mais 1 concha; misture; decore com 6 mini Oreo.</t>
+  </si>
+  <si>
+    <t>mix_twist_laka_oreo.jpg</t>
+  </si>
+  <si>
+    <t>Mix Twist Ouro Branco</t>
+  </si>
+  <si>
+    <t>Recheio Ganache Chocolate Branco Vabene; Sorvete misto; Bombom Ouro Branco</t>
+  </si>
+  <si>
+    <t>Coloque um pouco de sorvete; 1 concha de ganache branco; misture; complete; mais 1 concha; misture; decore com 1 bombom em 4 partes.</t>
+  </si>
+  <si>
+    <t>mix_twist_ouro_branco.jpg</t>
+  </si>
+  <si>
+    <t>Mix Twist Sonho de Valsa</t>
+  </si>
+  <si>
+    <t>Recheio Variegato Bombom Vabene; Sorvete de baunilha; Bombom Sonho de Valsa</t>
+  </si>
+  <si>
+    <t>Coloque um pouco de sorvete; 1 concha de variegato; misture; complete; mais 1 concha; misture; decore com bombom em 4 partes.</t>
+  </si>
+  <si>
+    <t>mix_twist_sonho_valsa.jpg</t>
+  </si>
+  <si>
+    <t>Mix Twist Pistache</t>
+  </si>
+  <si>
+    <t>Sorvete de baunilha; Creme de pistache; Castanha de caju crua</t>
+  </si>
+  <si>
+    <t>Preencha o pote até a metade com sorvete; adicione 1 concha de creme de pistache e misture até ficar homogêneo; conclua repetindo o processo; finalize com 1 medida D de castanha de caju por cima do sorvete.</t>
+  </si>
+  <si>
+    <t>mix_twist_pistache.jpg</t>
+  </si>
+  <si>
+    <t>Casquinha de Açaí</t>
+  </si>
+  <si>
+    <t>Casquinha</t>
+  </si>
+  <si>
+    <t>Açaí; Granola</t>
+  </si>
+  <si>
+    <t>Pegue a casquinha; coloque o açaí fazendo bico; finalize com granola (1 medida D) ao redor.</t>
+  </si>
+  <si>
+    <t>acai_casquinha.jpg</t>
+  </si>
+  <si>
+    <t>Açaí Sundae</t>
+  </si>
+  <si>
+    <t>175ml / 270ml</t>
+  </si>
+  <si>
+    <t>Açaí; Cobertura desejada (ou leite condensado)</t>
+  </si>
+  <si>
+    <t>Decore o copo com a cobertura desejada; coloque o açaí fazendo bico; finalize decorando com a cobertura escolhida ou granola.</t>
+  </si>
+  <si>
+    <t>acai_sundae.jpg</t>
   </si>
   <si>
     <t>Açaí Shake</t>
   </si>
   <si>
-    <t>Mix Kids</t>
+    <t>Açaí; Cobertura escolhida (abacaxi, amora, framboesa, maracujá, morango, limão) ou leite condensado</t>
+  </si>
+  <si>
+    <t>Coloque o açaí no copo; adicione as conchas de cobertura de fruta escolhida (ou leite condensado); misture com o batedor.</t>
+  </si>
+  <si>
+    <t>acai_shake.jpg</t>
+  </si>
+  <si>
+    <t>Açaí no Pote</t>
+  </si>
+  <si>
+    <t>240ml / Cestinha</t>
+  </si>
+  <si>
+    <t>Açaí; Cobertura desejada; Frutas opcionais (banana, morango, manga, uva, kiwi)</t>
+  </si>
+  <si>
+    <t>Coloque o açaí no pote fazendo bico; acrescente a fruta cortada; finalize com a cobertura escolhida.</t>
+  </si>
+  <si>
+    <t>acai_pote.jpg</t>
+  </si>
+  <si>
+    <t>Sundae / Big Sundae</t>
+  </si>
+  <si>
+    <t>Sundae de Pistache</t>
+  </si>
+  <si>
+    <t>Sorvete de baunilha; Creme de pistache; Castanha de caju crua; Biju</t>
+  </si>
+  <si>
+    <t>Coloque o sorvete no copo fazendo bico; finalize com 1 concha de creme de pistache, 1 medida D de castanha de caju e 1 biju.</t>
+  </si>
+  <si>
+    <t>Big Sundae: 2 conchas de creme e 2 bijus.</t>
+  </si>
+  <si>
+    <t>sundae_pistache.jpg</t>
+  </si>
+  <si>
+    <t>Nacho</t>
+  </si>
+  <si>
+    <t>Nacho Pistache</t>
+  </si>
+  <si>
+    <t>Único</t>
+  </si>
+  <si>
+    <t>Sorvete de baunilha; Creme de pistache; Castanha de caju crua; Biscoito Marvi</t>
+  </si>
+  <si>
+    <t>Coloque 3 voltas de sorvete na embalagem formando um bico; posicione 5 biscoitos Marvi ao redor; finalize com 1 concha de creme de pistache em volta do sorvete e 1 medida D de castanha de caju sobre o sorvete.</t>
+  </si>
+  <si>
+    <t>nacho_pistache.jpg</t>
+  </si>
+  <si>
+    <t>Chocolate Branco</t>
+  </si>
+  <si>
+    <t>Chocomenta</t>
+  </si>
+  <si>
+    <t>Choquito</t>
+  </si>
+  <si>
+    <t>Confeti</t>
+  </si>
+  <si>
+    <t>Danoninho</t>
+  </si>
+  <si>
+    <t>Framboesa</t>
+  </si>
+  <si>
+    <t>Iogurte</t>
+  </si>
+  <si>
+    <t>Kinder Ovo</t>
+  </si>
+  <si>
+    <t>Leite Condensado</t>
+  </si>
+  <si>
+    <t>Limao</t>
+  </si>
+  <si>
+    <t>Maracuja</t>
+  </si>
+  <si>
+    <t>Melancia</t>
+  </si>
+  <si>
+    <t>Milho</t>
+  </si>
+  <si>
+    <t>Milk Boll</t>
   </si>
   <si>
     <t>Morango</t>
   </si>
   <si>
-    <t>Proibido com Nutella</t>
+    <t>Negresco</t>
+  </si>
+  <si>
+    <t>Crocante</t>
+  </si>
+  <si>
+    <t>Pacoca</t>
+  </si>
+  <si>
+    <t>Passas ao Rum</t>
+  </si>
+  <si>
+    <t>Pe de Moleque</t>
   </si>
   <si>
     <t>Pistache</t>
   </si>
   <si>
-    <t>Maracujá</t>
-  </si>
-  <si>
-    <t>KitKat</t>
-  </si>
-  <si>
-    <t>Caramelo</t>
-  </si>
-  <si>
-    <t>Framboesa</t>
-  </si>
-  <si>
-    <t>Fini</t>
-  </si>
-  <si>
-    <t>250ml</t>
-  </si>
-  <si>
-    <t>400ml</t>
-  </si>
-  <si>
-    <t>500ml</t>
-  </si>
-  <si>
-    <t>700ml</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Leite, sorvete de morango, calda de morango</t>
-  </si>
-  <si>
-    <t>Leite, sorvete de pistache, cobertura</t>
-  </si>
-  <si>
-    <t>Leite, sorvete de creme, polpa de maracujá</t>
-  </si>
-  <si>
-    <t>Leite, sorvete de chocolate, pedaços de KitKat</t>
-  </si>
-  <si>
-    <t>Sorvete, calda de caramelo, chantilly</t>
-  </si>
-  <si>
-    <t>Açaí, leite, sorvete de creme, framboesa</t>
-  </si>
-  <si>
-    <t>Leite, sorvete de creme, balas Fini</t>
-  </si>
-  <si>
-    <t>Bater tudo no liquidificador</t>
-  </si>
-  <si>
-    <t>Bater no liquidificador e decorar com Nutella</t>
-  </si>
-  <si>
-    <t>Misturar e servir</t>
-  </si>
-  <si>
-    <t>Bater e servir</t>
-  </si>
-  <si>
-    <t>Bater e decorar com pedaços</t>
-  </si>
-  <si>
-    <t>Montar em camadas</t>
-  </si>
-  <si>
-    <t>Bater e servir com balas por cima</t>
-  </si>
-  <si>
-    <t>morango.jpg</t>
-  </si>
-  <si>
-    <t>nutella.jpg</t>
-  </si>
-  <si>
-    <t>pistache.jpg</t>
-  </si>
-  <si>
-    <t>maracuja.jpg</t>
-  </si>
-  <si>
-    <t>kitkat.jpg</t>
-  </si>
-  <si>
-    <t>caramelo.jpg</t>
-  </si>
-  <si>
-    <t>framboesa.jpg</t>
-  </si>
-  <si>
-    <t>fini.jpg</t>
-  </si>
-  <si>
-    <t>02 Medidas de Nutella; 02 Medidas de Ovomaltine</t>
-  </si>
-  <si>
-    <t>03 Medidas de Nutella; 03 Medidas de Ovomaltine</t>
-  </si>
-  <si>
-    <t>04 Medidas de Nutella; 04 Medidas de Ovomaltine</t>
-  </si>
-  <si>
-    <t>05 Medidas de Nutella; 05 Medidas de Ovomaltine</t>
-  </si>
-  <si>
-    <t>Nutella</t>
-  </si>
-  <si>
-    <t>02 Medidas de Nutella;</t>
-  </si>
-  <si>
-    <t>03 Medidas de Nutella;</t>
-  </si>
-  <si>
-    <t>04 Medidas de Nutella;</t>
-  </si>
-  <si>
-    <t>05 Medidas de Nutella;</t>
+    <t>Prestigio</t>
+  </si>
+  <si>
+    <t>Sensação</t>
+  </si>
+  <si>
+    <t>Farinha Lactea</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -228,7 +907,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -236,30 +915,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -278,9 +939,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -318,7 +979,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -352,7 +1013,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -387,10 +1047,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -564,37 +1223,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G286"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="41.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="70" customWidth="1"/>
+    <col min="5" max="5" width="95" customWidth="1"/>
+    <col min="6" max="6" width="42" customWidth="1"/>
+    <col min="7" max="7" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -603,19 +1263,19 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -623,19 +1283,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -643,19 +1303,19 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -663,362 +1323,4142 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="G6" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="G7" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="G8" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="G9" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" t="s">
         <v>23</v>
-      </c>
-      <c r="D10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E10" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="G11" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="G12" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="E13" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="G13" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" t="s">
         <v>27</v>
       </c>
-      <c r="D14" t="s">
-        <v>29</v>
-      </c>
-      <c r="E14" t="s">
-        <v>37</v>
-      </c>
       <c r="G14" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" t="s">
         <v>27</v>
       </c>
-      <c r="D15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E15" t="s">
-        <v>38</v>
-      </c>
       <c r="G15" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" t="s">
         <v>27</v>
       </c>
-      <c r="D16" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" t="s">
-        <v>39</v>
-      </c>
       <c r="G16" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" t="s">
         <v>27</v>
       </c>
-      <c r="D17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E17" t="s">
-        <v>40</v>
-      </c>
       <c r="G17" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C18" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E18" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G18" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E19" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G19" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E20" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G20" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D21" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E21" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G21" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D22" t="s">
         <v>34</v>
       </c>
       <c r="E22" t="s">
+        <v>35</v>
+      </c>
+      <c r="G22" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" t="s">
+        <v>34</v>
+      </c>
+      <c r="E23" t="s">
+        <v>35</v>
+      </c>
+      <c r="G23" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" t="s">
+        <v>35</v>
+      </c>
+      <c r="G24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" t="s">
+        <v>35</v>
+      </c>
+      <c r="G25" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" t="s">
+        <v>38</v>
+      </c>
+      <c r="E26" t="s">
+        <v>39</v>
+      </c>
+      <c r="G26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" t="s">
+        <v>37</v>
+      </c>
+      <c r="C27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" t="s">
+        <v>38</v>
+      </c>
+      <c r="E27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" t="s">
+        <v>39</v>
+      </c>
+      <c r="G28" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E29" t="s">
+        <v>39</v>
+      </c>
+      <c r="G29" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" t="s">
         <v>41</v>
       </c>
-      <c r="G22" t="s">
+      <c r="C30" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" t="s">
+        <v>42</v>
+      </c>
+      <c r="E30" t="s">
+        <v>43</v>
+      </c>
+      <c r="G30" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" t="s">
+        <v>42</v>
+      </c>
+      <c r="E31" t="s">
+        <v>43</v>
+      </c>
+      <c r="G31" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" t="s">
+        <v>14</v>
+      </c>
+      <c r="D32" t="s">
+        <v>42</v>
+      </c>
+      <c r="E32" t="s">
+        <v>43</v>
+      </c>
+      <c r="G32" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" t="s">
+        <v>42</v>
+      </c>
+      <c r="E33" t="s">
+        <v>43</v>
+      </c>
+      <c r="G33" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" t="s">
+        <v>47</v>
+      </c>
+      <c r="G34" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" t="s">
+        <v>45</v>
+      </c>
+      <c r="C35" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" t="s">
+        <v>46</v>
+      </c>
+      <c r="E35" t="s">
+        <v>47</v>
+      </c>
+      <c r="G35" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" t="s">
+        <v>14</v>
+      </c>
+      <c r="D36" t="s">
+        <v>46</v>
+      </c>
+      <c r="E36" t="s">
+        <v>47</v>
+      </c>
+      <c r="G36" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" t="s">
+        <v>46</v>
+      </c>
+      <c r="E37" t="s">
+        <v>47</v>
+      </c>
+      <c r="G37" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" t="s">
         <v>49</v>
       </c>
+      <c r="C38" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" t="s">
+        <v>50</v>
+      </c>
+      <c r="E38" t="s">
+        <v>51</v>
+      </c>
+      <c r="G38" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" t="s">
+        <v>49</v>
+      </c>
+      <c r="C39" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" t="s">
+        <v>50</v>
+      </c>
+      <c r="E39" t="s">
+        <v>51</v>
+      </c>
+      <c r="G39" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>7</v>
+      </c>
+      <c r="B40" t="s">
+        <v>49</v>
+      </c>
+      <c r="C40" t="s">
+        <v>14</v>
+      </c>
+      <c r="D40" t="s">
+        <v>50</v>
+      </c>
+      <c r="E40" t="s">
+        <v>51</v>
+      </c>
+      <c r="G40" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" t="s">
+        <v>49</v>
+      </c>
+      <c r="C41" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" t="s">
+        <v>50</v>
+      </c>
+      <c r="E41" t="s">
+        <v>51</v>
+      </c>
+      <c r="G41" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" t="s">
+        <v>54</v>
+      </c>
+      <c r="E42" t="s">
+        <v>55</v>
+      </c>
+      <c r="G42" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" t="s">
+        <v>53</v>
+      </c>
+      <c r="C43" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" t="s">
+        <v>54</v>
+      </c>
+      <c r="E43" t="s">
+        <v>55</v>
+      </c>
+      <c r="G43" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>7</v>
+      </c>
+      <c r="B44" t="s">
+        <v>53</v>
+      </c>
+      <c r="C44" t="s">
+        <v>14</v>
+      </c>
+      <c r="D44" t="s">
+        <v>54</v>
+      </c>
+      <c r="E44" t="s">
+        <v>55</v>
+      </c>
+      <c r="G44" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45" t="s">
+        <v>53</v>
+      </c>
+      <c r="C45" t="s">
+        <v>15</v>
+      </c>
+      <c r="D45" t="s">
+        <v>54</v>
+      </c>
+      <c r="E45" t="s">
+        <v>55</v>
+      </c>
+      <c r="G45" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" t="s">
+        <v>58</v>
+      </c>
+      <c r="E46" t="s">
+        <v>59</v>
+      </c>
+      <c r="G46" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47" t="s">
+        <v>57</v>
+      </c>
+      <c r="C47" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" t="s">
+        <v>58</v>
+      </c>
+      <c r="E47" t="s">
+        <v>59</v>
+      </c>
+      <c r="G47" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" t="s">
+        <v>57</v>
+      </c>
+      <c r="C48" t="s">
+        <v>14</v>
+      </c>
+      <c r="D48" t="s">
+        <v>58</v>
+      </c>
+      <c r="E48" t="s">
+        <v>59</v>
+      </c>
+      <c r="G48" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>7</v>
+      </c>
+      <c r="B49" t="s">
+        <v>57</v>
+      </c>
+      <c r="C49" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" t="s">
+        <v>58</v>
+      </c>
+      <c r="E49" t="s">
+        <v>59</v>
+      </c>
+      <c r="G49" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>7</v>
+      </c>
+      <c r="B50" t="s">
+        <v>61</v>
+      </c>
+      <c r="C50" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" t="s">
+        <v>62</v>
+      </c>
+      <c r="E50" t="s">
+        <v>63</v>
+      </c>
+      <c r="G50" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>7</v>
+      </c>
+      <c r="B51" t="s">
+        <v>61</v>
+      </c>
+      <c r="C51" t="s">
+        <v>13</v>
+      </c>
+      <c r="D51" t="s">
+        <v>62</v>
+      </c>
+      <c r="E51" t="s">
+        <v>63</v>
+      </c>
+      <c r="G51" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>7</v>
+      </c>
+      <c r="B52" t="s">
+        <v>61</v>
+      </c>
+      <c r="C52" t="s">
+        <v>14</v>
+      </c>
+      <c r="D52" t="s">
+        <v>62</v>
+      </c>
+      <c r="E52" t="s">
+        <v>63</v>
+      </c>
+      <c r="G52" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53" t="s">
+        <v>61</v>
+      </c>
+      <c r="C53" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" t="s">
+        <v>62</v>
+      </c>
+      <c r="E53" t="s">
+        <v>63</v>
+      </c>
+      <c r="G53" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" t="s">
+        <v>65</v>
+      </c>
+      <c r="C54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" t="s">
+        <v>66</v>
+      </c>
+      <c r="E54" t="s">
+        <v>67</v>
+      </c>
+      <c r="G54" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55" t="s">
+        <v>65</v>
+      </c>
+      <c r="C55" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" t="s">
+        <v>66</v>
+      </c>
+      <c r="E55" t="s">
+        <v>67</v>
+      </c>
+      <c r="G55" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>7</v>
+      </c>
+      <c r="B56" t="s">
+        <v>65</v>
+      </c>
+      <c r="C56" t="s">
+        <v>14</v>
+      </c>
+      <c r="D56" t="s">
+        <v>66</v>
+      </c>
+      <c r="E56" t="s">
+        <v>67</v>
+      </c>
+      <c r="G56" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>7</v>
+      </c>
+      <c r="B57" t="s">
+        <v>65</v>
+      </c>
+      <c r="C57" t="s">
+        <v>15</v>
+      </c>
+      <c r="D57" t="s">
+        <v>66</v>
+      </c>
+      <c r="E57" t="s">
+        <v>67</v>
+      </c>
+      <c r="G57" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>7</v>
+      </c>
+      <c r="B58" t="s">
+        <v>69</v>
+      </c>
+      <c r="C58" t="s">
+        <v>9</v>
+      </c>
+      <c r="F58" t="s">
+        <v>71</v>
+      </c>
+      <c r="G58" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>7</v>
+      </c>
+      <c r="B59" t="s">
+        <v>69</v>
+      </c>
+      <c r="C59" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>7</v>
+      </c>
+      <c r="B60" t="s">
+        <v>69</v>
+      </c>
+      <c r="C60" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>7</v>
+      </c>
+      <c r="B61" t="s">
+        <v>69</v>
+      </c>
+      <c r="C61" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>7</v>
+      </c>
+      <c r="B62" t="s">
+        <v>73</v>
+      </c>
+      <c r="C62" t="s">
+        <v>9</v>
+      </c>
+      <c r="F62" t="s">
+        <v>71</v>
+      </c>
+      <c r="G62" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>7</v>
+      </c>
+      <c r="B63" t="s">
+        <v>73</v>
+      </c>
+      <c r="C63" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>7</v>
+      </c>
+      <c r="B64" t="s">
+        <v>73</v>
+      </c>
+      <c r="C64" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>7</v>
+      </c>
+      <c r="B65" t="s">
+        <v>73</v>
+      </c>
+      <c r="C65" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>7</v>
+      </c>
+      <c r="B66" t="s">
+        <v>264</v>
+      </c>
+      <c r="C66" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>7</v>
+      </c>
+      <c r="B67" t="s">
+        <v>264</v>
+      </c>
+      <c r="C67" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>7</v>
+      </c>
+      <c r="B68" t="s">
+        <v>264</v>
+      </c>
+      <c r="C68" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>7</v>
+      </c>
+      <c r="B69" t="s">
+        <v>264</v>
+      </c>
+      <c r="C69" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>7</v>
+      </c>
+      <c r="B70" t="s">
+        <v>265</v>
+      </c>
+      <c r="C70" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>7</v>
+      </c>
+      <c r="B71" t="s">
+        <v>265</v>
+      </c>
+      <c r="C71" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>7</v>
+      </c>
+      <c r="B72" t="s">
+        <v>265</v>
+      </c>
+      <c r="C72" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>7</v>
+      </c>
+      <c r="B73" t="s">
+        <v>265</v>
+      </c>
+      <c r="C73" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>7</v>
+      </c>
+      <c r="B74" t="s">
+        <v>266</v>
+      </c>
+      <c r="C74" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>7</v>
+      </c>
+      <c r="B75" t="s">
+        <v>266</v>
+      </c>
+      <c r="C75" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>7</v>
+      </c>
+      <c r="B76" t="s">
+        <v>266</v>
+      </c>
+      <c r="C76" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>7</v>
+      </c>
+      <c r="B77" t="s">
+        <v>266</v>
+      </c>
+      <c r="C77" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>7</v>
+      </c>
+      <c r="B78" t="s">
+        <v>75</v>
+      </c>
+      <c r="C78" t="s">
+        <v>9</v>
+      </c>
+      <c r="F78" t="s">
+        <v>71</v>
+      </c>
+      <c r="G78" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>7</v>
+      </c>
+      <c r="B79" t="s">
+        <v>75</v>
+      </c>
+      <c r="C79" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>7</v>
+      </c>
+      <c r="B80" t="s">
+        <v>75</v>
+      </c>
+      <c r="C80" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>7</v>
+      </c>
+      <c r="B81" t="s">
+        <v>75</v>
+      </c>
+      <c r="C81" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>7</v>
+      </c>
+      <c r="B82" t="s">
+        <v>267</v>
+      </c>
+      <c r="C82" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>7</v>
+      </c>
+      <c r="B83" t="s">
+        <v>267</v>
+      </c>
+      <c r="C83" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>7</v>
+      </c>
+      <c r="B84" t="s">
+        <v>267</v>
+      </c>
+      <c r="C84" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>7</v>
+      </c>
+      <c r="B85" t="s">
+        <v>267</v>
+      </c>
+      <c r="C85" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>7</v>
+      </c>
+      <c r="B86" t="s">
+        <v>77</v>
+      </c>
+      <c r="C86" t="s">
+        <v>9</v>
+      </c>
+      <c r="F86" t="s">
+        <v>71</v>
+      </c>
+      <c r="G86" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>7</v>
+      </c>
+      <c r="B87" t="s">
+        <v>77</v>
+      </c>
+      <c r="C87" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>7</v>
+      </c>
+      <c r="B88" t="s">
+        <v>77</v>
+      </c>
+      <c r="C88" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>7</v>
+      </c>
+      <c r="B89" t="s">
+        <v>77</v>
+      </c>
+      <c r="C89" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>7</v>
+      </c>
+      <c r="B90" t="s">
+        <v>268</v>
+      </c>
+      <c r="C90" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>7</v>
+      </c>
+      <c r="B91" t="s">
+        <v>268</v>
+      </c>
+      <c r="C91" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>7</v>
+      </c>
+      <c r="B92" t="s">
+        <v>268</v>
+      </c>
+      <c r="C92" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>7</v>
+      </c>
+      <c r="B93" t="s">
+        <v>268</v>
+      </c>
+      <c r="C93" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>7</v>
+      </c>
+      <c r="B94" t="s">
+        <v>112</v>
+      </c>
+      <c r="C94" t="s">
+        <v>9</v>
+      </c>
+      <c r="F94" t="s">
+        <v>113</v>
+      </c>
+      <c r="G94" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>7</v>
+      </c>
+      <c r="B95" t="s">
+        <v>112</v>
+      </c>
+      <c r="C95" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>7</v>
+      </c>
+      <c r="B96" t="s">
+        <v>112</v>
+      </c>
+      <c r="C96" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>7</v>
+      </c>
+      <c r="B97" t="s">
+        <v>112</v>
+      </c>
+      <c r="C97" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>7</v>
+      </c>
+      <c r="B98" t="s">
+        <v>79</v>
+      </c>
+      <c r="C98" t="s">
+        <v>9</v>
+      </c>
+      <c r="F98" t="s">
+        <v>71</v>
+      </c>
+      <c r="G98" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>7</v>
+      </c>
+      <c r="B99" t="s">
+        <v>79</v>
+      </c>
+      <c r="C99" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>7</v>
+      </c>
+      <c r="B100" t="s">
+        <v>79</v>
+      </c>
+      <c r="C100" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>7</v>
+      </c>
+      <c r="B101" t="s">
+        <v>79</v>
+      </c>
+      <c r="C101" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>7</v>
+      </c>
+      <c r="B102" t="s">
+        <v>269</v>
+      </c>
+      <c r="C102" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>7</v>
+      </c>
+      <c r="B103" t="s">
+        <v>269</v>
+      </c>
+      <c r="C103" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>7</v>
+      </c>
+      <c r="B104" t="s">
+        <v>269</v>
+      </c>
+      <c r="C104" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>7</v>
+      </c>
+      <c r="B105" t="s">
+        <v>269</v>
+      </c>
+      <c r="C105" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>7</v>
+      </c>
+      <c r="B106" t="s">
+        <v>270</v>
+      </c>
+      <c r="C106" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>7</v>
+      </c>
+      <c r="B107" t="s">
+        <v>270</v>
+      </c>
+      <c r="C107" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>7</v>
+      </c>
+      <c r="B108" t="s">
+        <v>270</v>
+      </c>
+      <c r="C108" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>7</v>
+      </c>
+      <c r="B109" t="s">
+        <v>270</v>
+      </c>
+      <c r="C109" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>7</v>
+      </c>
+      <c r="B110" t="s">
+        <v>271</v>
+      </c>
+      <c r="C110" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>7</v>
+      </c>
+      <c r="B111" t="s">
+        <v>271</v>
+      </c>
+      <c r="C111" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>7</v>
+      </c>
+      <c r="B112" t="s">
+        <v>271</v>
+      </c>
+      <c r="C112" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>7</v>
+      </c>
+      <c r="B113" t="s">
+        <v>271</v>
+      </c>
+      <c r="C113" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>7</v>
+      </c>
+      <c r="B114" t="s">
+        <v>272</v>
+      </c>
+      <c r="C114" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>7</v>
+      </c>
+      <c r="B115" t="s">
+        <v>272</v>
+      </c>
+      <c r="C115" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>7</v>
+      </c>
+      <c r="B116" t="s">
+        <v>272</v>
+      </c>
+      <c r="C116" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>7</v>
+      </c>
+      <c r="B117" t="s">
+        <v>272</v>
+      </c>
+      <c r="C117" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>7</v>
+      </c>
+      <c r="B118" t="s">
+        <v>273</v>
+      </c>
+      <c r="C118" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>7</v>
+      </c>
+      <c r="B119" t="s">
+        <v>273</v>
+      </c>
+      <c r="C119" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>7</v>
+      </c>
+      <c r="B120" t="s">
+        <v>273</v>
+      </c>
+      <c r="C120" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>7</v>
+      </c>
+      <c r="B121" t="s">
+        <v>273</v>
+      </c>
+      <c r="C121" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>7</v>
+      </c>
+      <c r="B122" t="s">
+        <v>274</v>
+      </c>
+      <c r="C122" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>7</v>
+      </c>
+      <c r="B123" t="s">
+        <v>274</v>
+      </c>
+      <c r="C123" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>7</v>
+      </c>
+      <c r="B124" t="s">
+        <v>274</v>
+      </c>
+      <c r="C124" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>7</v>
+      </c>
+      <c r="B125" t="s">
+        <v>274</v>
+      </c>
+      <c r="C125" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>7</v>
+      </c>
+      <c r="B126" t="s">
+        <v>275</v>
+      </c>
+      <c r="C126" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>7</v>
+      </c>
+      <c r="B127" t="s">
+        <v>275</v>
+      </c>
+      <c r="C127" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>7</v>
+      </c>
+      <c r="B128" t="s">
+        <v>275</v>
+      </c>
+      <c r="C128" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>7</v>
+      </c>
+      <c r="B129" t="s">
+        <v>275</v>
+      </c>
+      <c r="C129" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>7</v>
+      </c>
+      <c r="B130" t="s">
+        <v>81</v>
+      </c>
+      <c r="C130" t="s">
+        <v>9</v>
+      </c>
+      <c r="F130" t="s">
+        <v>71</v>
+      </c>
+      <c r="G130" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>7</v>
+      </c>
+      <c r="B131" t="s">
+        <v>81</v>
+      </c>
+      <c r="C131" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>7</v>
+      </c>
+      <c r="B132" t="s">
+        <v>81</v>
+      </c>
+      <c r="C132" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>7</v>
+      </c>
+      <c r="B133" t="s">
+        <v>81</v>
+      </c>
+      <c r="C133" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>7</v>
+      </c>
+      <c r="B134" t="s">
+        <v>276</v>
+      </c>
+      <c r="C134" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>7</v>
+      </c>
+      <c r="B135" t="s">
+        <v>276</v>
+      </c>
+      <c r="C135" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>7</v>
+      </c>
+      <c r="B136" t="s">
+        <v>276</v>
+      </c>
+      <c r="C136" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>7</v>
+      </c>
+      <c r="B137" t="s">
+        <v>276</v>
+      </c>
+      <c r="C137" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>7</v>
+      </c>
+      <c r="B138" t="s">
+        <v>277</v>
+      </c>
+      <c r="C138" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>7</v>
+      </c>
+      <c r="B139" t="s">
+        <v>277</v>
+      </c>
+      <c r="C139" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>7</v>
+      </c>
+      <c r="B140" t="s">
+        <v>277</v>
+      </c>
+      <c r="C140" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>7</v>
+      </c>
+      <c r="B141" t="s">
+        <v>277</v>
+      </c>
+      <c r="C141" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>7</v>
+      </c>
+      <c r="B142" t="s">
+        <v>278</v>
+      </c>
+      <c r="C142" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>7</v>
+      </c>
+      <c r="B143" t="s">
+        <v>278</v>
+      </c>
+      <c r="C143" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>7</v>
+      </c>
+      <c r="B144" t="s">
+        <v>278</v>
+      </c>
+      <c r="C144" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>7</v>
+      </c>
+      <c r="B145" t="s">
+        <v>278</v>
+      </c>
+      <c r="C145" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>7</v>
+      </c>
+      <c r="B146" t="s">
+        <v>83</v>
+      </c>
+      <c r="C146" t="s">
+        <v>9</v>
+      </c>
+      <c r="F146" t="s">
+        <v>71</v>
+      </c>
+      <c r="G146" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>7</v>
+      </c>
+      <c r="B147" t="s">
+        <v>83</v>
+      </c>
+      <c r="C147" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>7</v>
+      </c>
+      <c r="B148" t="s">
+        <v>83</v>
+      </c>
+      <c r="C148" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>7</v>
+      </c>
+      <c r="B149" t="s">
+        <v>83</v>
+      </c>
+      <c r="C149" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>7</v>
+      </c>
+      <c r="B150" t="s">
+        <v>279</v>
+      </c>
+      <c r="C150" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>7</v>
+      </c>
+      <c r="B151" t="s">
+        <v>279</v>
+      </c>
+      <c r="C151" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>7</v>
+      </c>
+      <c r="B152" t="s">
+        <v>279</v>
+      </c>
+      <c r="C152" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>7</v>
+      </c>
+      <c r="B153" t="s">
+        <v>279</v>
+      </c>
+      <c r="C153" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>7</v>
+      </c>
+      <c r="B154" t="s">
+        <v>280</v>
+      </c>
+      <c r="C154" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>7</v>
+      </c>
+      <c r="B155" t="s">
+        <v>280</v>
+      </c>
+      <c r="C155" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>7</v>
+      </c>
+      <c r="B156" t="s">
+        <v>280</v>
+      </c>
+      <c r="C156" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>7</v>
+      </c>
+      <c r="B157" t="s">
+        <v>280</v>
+      </c>
+      <c r="C157" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>7</v>
+      </c>
+      <c r="B158" t="s">
+        <v>281</v>
+      </c>
+      <c r="C158" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>7</v>
+      </c>
+      <c r="B159" t="s">
+        <v>281</v>
+      </c>
+      <c r="C159" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>7</v>
+      </c>
+      <c r="B160" t="s">
+        <v>281</v>
+      </c>
+      <c r="C160" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>7</v>
+      </c>
+      <c r="B161" t="s">
+        <v>281</v>
+      </c>
+      <c r="C161" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>7</v>
+      </c>
+      <c r="B162" t="s">
+        <v>282</v>
+      </c>
+      <c r="C162" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>7</v>
+      </c>
+      <c r="B163" t="s">
+        <v>282</v>
+      </c>
+      <c r="C163" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>7</v>
+      </c>
+      <c r="B164" t="s">
+        <v>282</v>
+      </c>
+      <c r="C164" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>7</v>
+      </c>
+      <c r="B165" t="s">
+        <v>282</v>
+      </c>
+      <c r="C165" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>7</v>
+      </c>
+      <c r="B166" t="s">
+        <v>283</v>
+      </c>
+      <c r="C166" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>7</v>
+      </c>
+      <c r="B167" t="s">
+        <v>283</v>
+      </c>
+      <c r="C167" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>7</v>
+      </c>
+      <c r="B168" t="s">
+        <v>283</v>
+      </c>
+      <c r="C168" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>7</v>
+      </c>
+      <c r="B169" t="s">
+        <v>283</v>
+      </c>
+      <c r="C169" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>7</v>
+      </c>
+      <c r="B170" t="s">
+        <v>284</v>
+      </c>
+      <c r="C170" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>7</v>
+      </c>
+      <c r="B171" t="s">
+        <v>284</v>
+      </c>
+      <c r="C171" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>7</v>
+      </c>
+      <c r="B172" t="s">
+        <v>284</v>
+      </c>
+      <c r="C172" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>7</v>
+      </c>
+      <c r="B173" t="s">
+        <v>284</v>
+      </c>
+      <c r="C173" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>7</v>
+      </c>
+      <c r="B174" t="s">
+        <v>285</v>
+      </c>
+      <c r="C174" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>7</v>
+      </c>
+      <c r="B175" t="s">
+        <v>285</v>
+      </c>
+      <c r="C175" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>7</v>
+      </c>
+      <c r="B176" t="s">
+        <v>285</v>
+      </c>
+      <c r="C176" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>7</v>
+      </c>
+      <c r="B177" t="s">
+        <v>285</v>
+      </c>
+      <c r="C177" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>7</v>
+      </c>
+      <c r="B178" t="s">
+        <v>286</v>
+      </c>
+      <c r="C178" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>7</v>
+      </c>
+      <c r="B179" t="s">
+        <v>286</v>
+      </c>
+      <c r="C179" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>7</v>
+      </c>
+      <c r="B180" t="s">
+        <v>286</v>
+      </c>
+      <c r="C180" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>7</v>
+      </c>
+      <c r="B181" t="s">
+        <v>286</v>
+      </c>
+      <c r="C181" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>7</v>
+      </c>
+      <c r="B182" t="s">
+        <v>85</v>
+      </c>
+      <c r="C182" t="s">
+        <v>9</v>
+      </c>
+      <c r="F182" t="s">
+        <v>71</v>
+      </c>
+      <c r="G182" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>7</v>
+      </c>
+      <c r="B183" t="s">
+        <v>85</v>
+      </c>
+      <c r="C183" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>7</v>
+      </c>
+      <c r="B184" t="s">
+        <v>85</v>
+      </c>
+      <c r="C184" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>7</v>
+      </c>
+      <c r="B185" t="s">
+        <v>85</v>
+      </c>
+      <c r="C185" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>87</v>
+      </c>
+      <c r="B186" t="s">
+        <v>287</v>
+      </c>
+      <c r="C186" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>87</v>
+      </c>
+      <c r="B187" t="s">
+        <v>287</v>
+      </c>
+      <c r="C187" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>87</v>
+      </c>
+      <c r="B188" t="s">
+        <v>287</v>
+      </c>
+      <c r="C188" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>87</v>
+      </c>
+      <c r="B189" t="s">
+        <v>287</v>
+      </c>
+      <c r="C189" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>87</v>
+      </c>
+      <c r="B190" t="s">
+        <v>115</v>
+      </c>
+      <c r="C190" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>87</v>
+      </c>
+      <c r="B191" t="s">
+        <v>115</v>
+      </c>
+      <c r="C191" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>87</v>
+      </c>
+      <c r="B192" t="s">
+        <v>115</v>
+      </c>
+      <c r="C192" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>87</v>
+      </c>
+      <c r="B193" t="s">
+        <v>115</v>
+      </c>
+      <c r="C193" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>87</v>
+      </c>
+      <c r="B194" t="s">
+        <v>116</v>
+      </c>
+      <c r="C194" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>87</v>
+      </c>
+      <c r="B195" t="s">
+        <v>116</v>
+      </c>
+      <c r="C195" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>87</v>
+      </c>
+      <c r="B196" t="s">
+        <v>116</v>
+      </c>
+      <c r="C196" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>87</v>
+      </c>
+      <c r="B197" t="s">
+        <v>116</v>
+      </c>
+      <c r="C197" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>87</v>
+      </c>
+      <c r="B198" t="s">
+        <v>117</v>
+      </c>
+      <c r="C198" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>87</v>
+      </c>
+      <c r="B199" t="s">
+        <v>117</v>
+      </c>
+      <c r="C199" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>87</v>
+      </c>
+      <c r="B200" t="s">
+        <v>117</v>
+      </c>
+      <c r="C200" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>87</v>
+      </c>
+      <c r="B201" t="s">
+        <v>117</v>
+      </c>
+      <c r="C201" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>87</v>
+      </c>
+      <c r="B202" t="s">
+        <v>118</v>
+      </c>
+      <c r="C202" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>87</v>
+      </c>
+      <c r="B203" t="s">
+        <v>118</v>
+      </c>
+      <c r="C203" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>87</v>
+      </c>
+      <c r="B204" t="s">
+        <v>118</v>
+      </c>
+      <c r="C204" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>87</v>
+      </c>
+      <c r="B205" t="s">
+        <v>118</v>
+      </c>
+      <c r="C205" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>87</v>
+      </c>
+      <c r="B206" t="s">
+        <v>119</v>
+      </c>
+      <c r="C206" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>87</v>
+      </c>
+      <c r="B207" t="s">
+        <v>119</v>
+      </c>
+      <c r="C207" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>87</v>
+      </c>
+      <c r="B208" t="s">
+        <v>119</v>
+      </c>
+      <c r="C208" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>87</v>
+      </c>
+      <c r="B209" t="s">
+        <v>119</v>
+      </c>
+      <c r="C209" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>87</v>
+      </c>
+      <c r="B210" t="s">
+        <v>120</v>
+      </c>
+      <c r="C210" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>87</v>
+      </c>
+      <c r="B211" t="s">
+        <v>120</v>
+      </c>
+      <c r="C211" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>87</v>
+      </c>
+      <c r="B212" t="s">
+        <v>120</v>
+      </c>
+      <c r="C212" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>87</v>
+      </c>
+      <c r="B213" t="s">
+        <v>120</v>
+      </c>
+      <c r="C213" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>87</v>
+      </c>
+      <c r="B214" t="s">
+        <v>121</v>
+      </c>
+      <c r="C214" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>87</v>
+      </c>
+      <c r="B215" t="s">
+        <v>121</v>
+      </c>
+      <c r="C215" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>87</v>
+      </c>
+      <c r="B216" t="s">
+        <v>121</v>
+      </c>
+      <c r="C216" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>87</v>
+      </c>
+      <c r="B217" t="s">
+        <v>121</v>
+      </c>
+      <c r="C217" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>87</v>
+      </c>
+      <c r="B218" t="s">
+        <v>122</v>
+      </c>
+      <c r="C218" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>87</v>
+      </c>
+      <c r="B219" t="s">
+        <v>122</v>
+      </c>
+      <c r="C219" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>87</v>
+      </c>
+      <c r="B220" t="s">
+        <v>122</v>
+      </c>
+      <c r="C220" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>87</v>
+      </c>
+      <c r="B221" t="s">
+        <v>122</v>
+      </c>
+      <c r="C221" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>87</v>
+      </c>
+      <c r="B222" t="s">
+        <v>123</v>
+      </c>
+      <c r="C222" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>87</v>
+      </c>
+      <c r="B223" t="s">
+        <v>123</v>
+      </c>
+      <c r="C223" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>87</v>
+      </c>
+      <c r="B224" t="s">
+        <v>123</v>
+      </c>
+      <c r="C224" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>87</v>
+      </c>
+      <c r="B225" t="s">
+        <v>123</v>
+      </c>
+      <c r="C225" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>87</v>
+      </c>
+      <c r="B226" t="s">
+        <v>124</v>
+      </c>
+      <c r="C226" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>87</v>
+      </c>
+      <c r="B227" t="s">
+        <v>124</v>
+      </c>
+      <c r="C227" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>87</v>
+      </c>
+      <c r="B228" t="s">
+        <v>124</v>
+      </c>
+      <c r="C228" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>87</v>
+      </c>
+      <c r="B229" t="s">
+        <v>124</v>
+      </c>
+      <c r="C229" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>87</v>
+      </c>
+      <c r="B230" t="s">
+        <v>92</v>
+      </c>
+      <c r="C230" t="s">
+        <v>9</v>
+      </c>
+      <c r="D230" t="s">
+        <v>93</v>
+      </c>
+      <c r="E230" t="s">
+        <v>94</v>
+      </c>
+      <c r="G230" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>87</v>
+      </c>
+      <c r="B231" t="s">
+        <v>92</v>
+      </c>
+      <c r="C231" t="s">
+        <v>13</v>
+      </c>
+      <c r="D231" t="s">
+        <v>93</v>
+      </c>
+      <c r="E231" t="s">
+        <v>94</v>
+      </c>
+      <c r="G231" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>87</v>
+      </c>
+      <c r="B232" t="s">
+        <v>92</v>
+      </c>
+      <c r="C232" t="s">
+        <v>14</v>
+      </c>
+      <c r="D232" t="s">
+        <v>93</v>
+      </c>
+      <c r="E232" t="s">
+        <v>94</v>
+      </c>
+      <c r="G232" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>87</v>
+      </c>
+      <c r="B233" t="s">
+        <v>92</v>
+      </c>
+      <c r="C233" t="s">
+        <v>15</v>
+      </c>
+      <c r="D233" t="s">
+        <v>93</v>
+      </c>
+      <c r="E233" t="s">
+        <v>94</v>
+      </c>
+      <c r="G233" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>87</v>
+      </c>
+      <c r="B234" t="s">
+        <v>88</v>
+      </c>
+      <c r="C234" t="s">
+        <v>9</v>
+      </c>
+      <c r="D234" t="s">
+        <v>89</v>
+      </c>
+      <c r="E234" t="s">
+        <v>90</v>
+      </c>
+      <c r="G234" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>87</v>
+      </c>
+      <c r="B235" t="s">
+        <v>88</v>
+      </c>
+      <c r="C235" t="s">
+        <v>13</v>
+      </c>
+      <c r="D235" t="s">
+        <v>89</v>
+      </c>
+      <c r="E235" t="s">
+        <v>90</v>
+      </c>
+      <c r="G235" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>87</v>
+      </c>
+      <c r="B236" t="s">
+        <v>88</v>
+      </c>
+      <c r="C236" t="s">
+        <v>14</v>
+      </c>
+      <c r="D236" t="s">
+        <v>89</v>
+      </c>
+      <c r="E236" t="s">
+        <v>90</v>
+      </c>
+      <c r="G236" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>87</v>
+      </c>
+      <c r="B237" t="s">
+        <v>88</v>
+      </c>
+      <c r="C237" t="s">
+        <v>15</v>
+      </c>
+      <c r="D237" t="s">
+        <v>89</v>
+      </c>
+      <c r="E237" t="s">
+        <v>90</v>
+      </c>
+      <c r="G237" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>87</v>
+      </c>
+      <c r="B238" t="s">
+        <v>96</v>
+      </c>
+      <c r="C238" t="s">
+        <v>9</v>
+      </c>
+      <c r="D238" t="s">
+        <v>97</v>
+      </c>
+      <c r="E238" t="s">
+        <v>98</v>
+      </c>
+      <c r="G238" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>87</v>
+      </c>
+      <c r="B239" t="s">
+        <v>96</v>
+      </c>
+      <c r="C239" t="s">
+        <v>13</v>
+      </c>
+      <c r="D239" t="s">
+        <v>97</v>
+      </c>
+      <c r="E239" t="s">
+        <v>98</v>
+      </c>
+      <c r="G239" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>87</v>
+      </c>
+      <c r="B240" t="s">
+        <v>96</v>
+      </c>
+      <c r="C240" t="s">
+        <v>14</v>
+      </c>
+      <c r="D240" t="s">
+        <v>97</v>
+      </c>
+      <c r="E240" t="s">
+        <v>98</v>
+      </c>
+      <c r="G240" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>87</v>
+      </c>
+      <c r="B241" t="s">
+        <v>96</v>
+      </c>
+      <c r="C241" t="s">
+        <v>15</v>
+      </c>
+      <c r="D241" t="s">
+        <v>97</v>
+      </c>
+      <c r="E241" t="s">
+        <v>98</v>
+      </c>
+      <c r="G241" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>87</v>
+      </c>
+      <c r="B242" t="s">
+        <v>100</v>
+      </c>
+      <c r="C242" t="s">
+        <v>9</v>
+      </c>
+      <c r="D242" t="s">
+        <v>101</v>
+      </c>
+      <c r="E242" t="s">
+        <v>102</v>
+      </c>
+      <c r="G242" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>87</v>
+      </c>
+      <c r="B243" t="s">
+        <v>100</v>
+      </c>
+      <c r="C243" t="s">
+        <v>13</v>
+      </c>
+      <c r="D243" t="s">
+        <v>101</v>
+      </c>
+      <c r="E243" t="s">
+        <v>102</v>
+      </c>
+      <c r="G243" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>87</v>
+      </c>
+      <c r="B244" t="s">
+        <v>100</v>
+      </c>
+      <c r="C244" t="s">
+        <v>14</v>
+      </c>
+      <c r="D244" t="s">
+        <v>101</v>
+      </c>
+      <c r="E244" t="s">
+        <v>102</v>
+      </c>
+      <c r="G244" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>87</v>
+      </c>
+      <c r="B245" t="s">
+        <v>100</v>
+      </c>
+      <c r="C245" t="s">
+        <v>15</v>
+      </c>
+      <c r="D245" t="s">
+        <v>101</v>
+      </c>
+      <c r="E245" t="s">
+        <v>102</v>
+      </c>
+      <c r="G245" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>87</v>
+      </c>
+      <c r="B246" t="s">
+        <v>104</v>
+      </c>
+      <c r="C246" t="s">
+        <v>9</v>
+      </c>
+      <c r="D246" t="s">
+        <v>105</v>
+      </c>
+      <c r="E246" t="s">
+        <v>106</v>
+      </c>
+      <c r="G246" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>87</v>
+      </c>
+      <c r="B247" t="s">
+        <v>104</v>
+      </c>
+      <c r="C247" t="s">
+        <v>13</v>
+      </c>
+      <c r="D247" t="s">
+        <v>105</v>
+      </c>
+      <c r="E247" t="s">
+        <v>106</v>
+      </c>
+      <c r="G247" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>87</v>
+      </c>
+      <c r="B248" t="s">
+        <v>104</v>
+      </c>
+      <c r="C248" t="s">
+        <v>14</v>
+      </c>
+      <c r="D248" t="s">
+        <v>105</v>
+      </c>
+      <c r="E248" t="s">
+        <v>106</v>
+      </c>
+      <c r="G248" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>87</v>
+      </c>
+      <c r="B249" t="s">
+        <v>104</v>
+      </c>
+      <c r="C249" t="s">
+        <v>15</v>
+      </c>
+      <c r="D249" t="s">
+        <v>105</v>
+      </c>
+      <c r="E249" t="s">
+        <v>106</v>
+      </c>
+      <c r="G249" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>87</v>
+      </c>
+      <c r="B250" t="s">
+        <v>108</v>
+      </c>
+      <c r="C250" t="s">
+        <v>9</v>
+      </c>
+      <c r="D250" t="s">
+        <v>109</v>
+      </c>
+      <c r="E250" t="s">
+        <v>110</v>
+      </c>
+      <c r="G250" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>87</v>
+      </c>
+      <c r="B251" t="s">
+        <v>108</v>
+      </c>
+      <c r="C251" t="s">
+        <v>13</v>
+      </c>
+      <c r="D251" t="s">
+        <v>109</v>
+      </c>
+      <c r="E251" t="s">
+        <v>110</v>
+      </c>
+      <c r="G251" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>87</v>
+      </c>
+      <c r="B252" t="s">
+        <v>108</v>
+      </c>
+      <c r="C252" t="s">
+        <v>14</v>
+      </c>
+      <c r="D252" t="s">
+        <v>109</v>
+      </c>
+      <c r="E252" t="s">
+        <v>110</v>
+      </c>
+      <c r="G252" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>87</v>
+      </c>
+      <c r="B253" t="s">
+        <v>108</v>
+      </c>
+      <c r="C253" t="s">
+        <v>15</v>
+      </c>
+      <c r="D253" t="s">
+        <v>109</v>
+      </c>
+      <c r="E253" t="s">
+        <v>110</v>
+      </c>
+      <c r="G253" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>125</v>
+      </c>
+      <c r="B254" t="s">
+        <v>126</v>
+      </c>
+      <c r="C254" t="s">
+        <v>127</v>
+      </c>
+      <c r="D254" t="s">
+        <v>128</v>
+      </c>
+      <c r="E254" t="s">
+        <v>129</v>
+      </c>
+      <c r="G254" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>125</v>
+      </c>
+      <c r="B255" t="s">
+        <v>131</v>
+      </c>
+      <c r="C255" t="s">
+        <v>127</v>
+      </c>
+      <c r="D255" t="s">
+        <v>132</v>
+      </c>
+      <c r="E255" t="s">
+        <v>133</v>
+      </c>
+      <c r="G255" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>125</v>
+      </c>
+      <c r="B256" t="s">
+        <v>135</v>
+      </c>
+      <c r="C256" t="s">
+        <v>127</v>
+      </c>
+      <c r="D256" t="s">
+        <v>136</v>
+      </c>
+      <c r="E256" t="s">
+        <v>137</v>
+      </c>
+      <c r="G256" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>139</v>
+      </c>
+      <c r="B257" t="s">
+        <v>140</v>
+      </c>
+      <c r="C257" t="s">
+        <v>127</v>
+      </c>
+      <c r="D257" t="s">
+        <v>141</v>
+      </c>
+      <c r="E257" t="s">
+        <v>142</v>
+      </c>
+      <c r="G257" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>139</v>
+      </c>
+      <c r="B258" t="s">
+        <v>144</v>
+      </c>
+      <c r="C258" t="s">
+        <v>127</v>
+      </c>
+      <c r="D258" t="s">
+        <v>145</v>
+      </c>
+      <c r="E258" t="s">
+        <v>146</v>
+      </c>
+      <c r="G258" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>139</v>
+      </c>
+      <c r="B259" t="s">
+        <v>148</v>
+      </c>
+      <c r="C259" t="s">
+        <v>127</v>
+      </c>
+      <c r="F259" t="s">
+        <v>113</v>
+      </c>
+      <c r="G259" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>139</v>
+      </c>
+      <c r="B260" t="s">
+        <v>150</v>
+      </c>
+      <c r="C260" t="s">
+        <v>127</v>
+      </c>
+      <c r="F260" t="s">
+        <v>113</v>
+      </c>
+      <c r="G260" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>139</v>
+      </c>
+      <c r="B261" t="s">
+        <v>152</v>
+      </c>
+      <c r="C261" t="s">
+        <v>127</v>
+      </c>
+      <c r="F261" t="s">
+        <v>113</v>
+      </c>
+      <c r="G261" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>154</v>
+      </c>
+      <c r="B262" t="s">
+        <v>155</v>
+      </c>
+      <c r="C262" t="s">
+        <v>127</v>
+      </c>
+      <c r="D262" t="s">
+        <v>156</v>
+      </c>
+      <c r="E262" t="s">
+        <v>157</v>
+      </c>
+      <c r="G262" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>154</v>
+      </c>
+      <c r="B263" t="s">
+        <v>159</v>
+      </c>
+      <c r="C263" t="s">
+        <v>127</v>
+      </c>
+      <c r="D263" t="s">
+        <v>160</v>
+      </c>
+      <c r="E263" t="s">
+        <v>161</v>
+      </c>
+      <c r="G263" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>154</v>
+      </c>
+      <c r="B264" t="s">
+        <v>163</v>
+      </c>
+      <c r="C264" t="s">
+        <v>127</v>
+      </c>
+      <c r="D264" t="s">
+        <v>164</v>
+      </c>
+      <c r="E264" t="s">
+        <v>165</v>
+      </c>
+      <c r="G264" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>154</v>
+      </c>
+      <c r="B265" t="s">
+        <v>167</v>
+      </c>
+      <c r="C265" t="s">
+        <v>127</v>
+      </c>
+      <c r="D265" t="s">
+        <v>168</v>
+      </c>
+      <c r="E265" t="s">
+        <v>169</v>
+      </c>
+      <c r="G265" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>154</v>
+      </c>
+      <c r="B266" t="s">
+        <v>171</v>
+      </c>
+      <c r="C266" t="s">
+        <v>127</v>
+      </c>
+      <c r="D266" t="s">
+        <v>172</v>
+      </c>
+      <c r="E266" t="s">
+        <v>173</v>
+      </c>
+      <c r="G266" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>175</v>
+      </c>
+      <c r="B267" t="s">
+        <v>176</v>
+      </c>
+      <c r="C267" t="s">
+        <v>177</v>
+      </c>
+      <c r="D267" t="s">
+        <v>178</v>
+      </c>
+      <c r="E267" t="s">
+        <v>179</v>
+      </c>
+      <c r="G267" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>175</v>
+      </c>
+      <c r="B268" t="s">
+        <v>181</v>
+      </c>
+      <c r="C268" t="s">
+        <v>177</v>
+      </c>
+      <c r="D268" t="s">
+        <v>182</v>
+      </c>
+      <c r="E268" t="s">
+        <v>183</v>
+      </c>
+      <c r="G268" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>175</v>
+      </c>
+      <c r="B269" t="s">
+        <v>185</v>
+      </c>
+      <c r="C269" t="s">
+        <v>177</v>
+      </c>
+      <c r="D269" t="s">
+        <v>186</v>
+      </c>
+      <c r="E269" t="s">
+        <v>187</v>
+      </c>
+      <c r="G269" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>175</v>
+      </c>
+      <c r="B270" t="s">
+        <v>189</v>
+      </c>
+      <c r="C270" t="s">
+        <v>177</v>
+      </c>
+      <c r="D270" t="s">
+        <v>190</v>
+      </c>
+      <c r="E270" t="s">
+        <v>191</v>
+      </c>
+      <c r="G270" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>175</v>
+      </c>
+      <c r="B271" t="s">
+        <v>193</v>
+      </c>
+      <c r="C271" t="s">
+        <v>177</v>
+      </c>
+      <c r="D271" t="s">
+        <v>194</v>
+      </c>
+      <c r="E271" t="s">
+        <v>195</v>
+      </c>
+      <c r="G271" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>175</v>
+      </c>
+      <c r="B272" t="s">
+        <v>197</v>
+      </c>
+      <c r="C272" t="s">
+        <v>177</v>
+      </c>
+      <c r="D272" t="s">
+        <v>198</v>
+      </c>
+      <c r="E272" t="s">
+        <v>199</v>
+      </c>
+      <c r="G272" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>175</v>
+      </c>
+      <c r="B273" t="s">
+        <v>201</v>
+      </c>
+      <c r="C273" t="s">
+        <v>177</v>
+      </c>
+      <c r="D273" t="s">
+        <v>202</v>
+      </c>
+      <c r="E273" t="s">
+        <v>203</v>
+      </c>
+      <c r="G273" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>175</v>
+      </c>
+      <c r="B274" t="s">
+        <v>205</v>
+      </c>
+      <c r="C274" t="s">
+        <v>177</v>
+      </c>
+      <c r="D274" t="s">
+        <v>206</v>
+      </c>
+      <c r="E274" t="s">
+        <v>207</v>
+      </c>
+      <c r="G274" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>175</v>
+      </c>
+      <c r="B275" t="s">
+        <v>209</v>
+      </c>
+      <c r="C275" t="s">
+        <v>177</v>
+      </c>
+      <c r="D275" t="s">
+        <v>210</v>
+      </c>
+      <c r="E275" t="s">
+        <v>211</v>
+      </c>
+      <c r="G275" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>175</v>
+      </c>
+      <c r="B276" t="s">
+        <v>213</v>
+      </c>
+      <c r="C276" t="s">
+        <v>177</v>
+      </c>
+      <c r="D276" t="s">
+        <v>214</v>
+      </c>
+      <c r="E276" t="s">
+        <v>215</v>
+      </c>
+      <c r="G276" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>175</v>
+      </c>
+      <c r="B277" t="s">
+        <v>217</v>
+      </c>
+      <c r="C277" t="s">
+        <v>177</v>
+      </c>
+      <c r="D277" t="s">
+        <v>218</v>
+      </c>
+      <c r="E277" t="s">
+        <v>219</v>
+      </c>
+      <c r="G277" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>175</v>
+      </c>
+      <c r="B278" t="s">
+        <v>221</v>
+      </c>
+      <c r="C278" t="s">
+        <v>177</v>
+      </c>
+      <c r="D278" t="s">
+        <v>222</v>
+      </c>
+      <c r="E278" t="s">
+        <v>223</v>
+      </c>
+      <c r="G278" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>175</v>
+      </c>
+      <c r="B279" t="s">
+        <v>225</v>
+      </c>
+      <c r="C279" t="s">
+        <v>177</v>
+      </c>
+      <c r="D279" t="s">
+        <v>226</v>
+      </c>
+      <c r="E279" t="s">
+        <v>227</v>
+      </c>
+      <c r="G279" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>175</v>
+      </c>
+      <c r="B280" t="s">
+        <v>229</v>
+      </c>
+      <c r="C280" t="s">
+        <v>177</v>
+      </c>
+      <c r="D280" t="s">
+        <v>230</v>
+      </c>
+      <c r="E280" t="s">
+        <v>231</v>
+      </c>
+      <c r="G280" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>24</v>
+      </c>
+      <c r="B281" t="s">
+        <v>233</v>
+      </c>
+      <c r="C281" t="s">
+        <v>234</v>
+      </c>
+      <c r="D281" t="s">
+        <v>235</v>
+      </c>
+      <c r="E281" t="s">
+        <v>236</v>
+      </c>
+      <c r="G281" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>24</v>
+      </c>
+      <c r="B282" t="s">
+        <v>238</v>
+      </c>
+      <c r="C282" t="s">
+        <v>239</v>
+      </c>
+      <c r="D282" t="s">
+        <v>240</v>
+      </c>
+      <c r="E282" t="s">
+        <v>241</v>
+      </c>
+      <c r="G282" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>24</v>
+      </c>
+      <c r="B283" t="s">
+        <v>243</v>
+      </c>
+      <c r="C283" t="s">
+        <v>70</v>
+      </c>
+      <c r="D283" t="s">
+        <v>244</v>
+      </c>
+      <c r="E283" t="s">
+        <v>245</v>
+      </c>
+      <c r="G283" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>24</v>
+      </c>
+      <c r="B284" t="s">
+        <v>247</v>
+      </c>
+      <c r="C284" t="s">
+        <v>248</v>
+      </c>
+      <c r="D284" t="s">
+        <v>249</v>
+      </c>
+      <c r="E284" t="s">
+        <v>250</v>
+      </c>
+      <c r="G284" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>252</v>
+      </c>
+      <c r="B285" t="s">
+        <v>253</v>
+      </c>
+      <c r="C285" t="s">
+        <v>239</v>
+      </c>
+      <c r="D285" t="s">
+        <v>254</v>
+      </c>
+      <c r="E285" t="s">
+        <v>255</v>
+      </c>
+      <c r="F285" t="s">
+        <v>256</v>
+      </c>
+      <c r="G285" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>258</v>
+      </c>
+      <c r="B286" t="s">
+        <v>259</v>
+      </c>
+      <c r="C286" t="s">
+        <v>260</v>
+      </c>
+      <c r="D286" t="s">
+        <v>261</v>
+      </c>
+      <c r="E286" t="s">
+        <v>262</v>
+      </c>
+      <c r="G286" t="s">
+        <v>263</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/modelo_receitas_atualizado.xlsx
+++ b/modelo_receitas_atualizado.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Usuario\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\walte\Desktop\MilkShakeMix_Cardapio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A939CE12-D99D-405D-9928-F1ACB136F930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{972E2437-9DF2-4263-B743-E71F1739D4CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="-45" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Receitas" sheetId="1" r:id="rId1"/>
@@ -22,27 +22,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1217" uniqueCount="288">
   <si>
-    <t>LINHA</t>
-  </si>
-  <si>
-    <t>PRODUTO</t>
-  </si>
-  <si>
-    <t>TAMANHO</t>
-  </si>
-  <si>
-    <t>INGREDIENTES</t>
-  </si>
-  <si>
-    <t>MODO DE PREPARO</t>
-  </si>
-  <si>
-    <t>OBSERVAÇÕES</t>
-  </si>
-  <si>
-    <t>IMAGEM</t>
-  </si>
-  <si>
     <t>Milkshakes Tradicionais</t>
   </si>
   <si>
@@ -884,6 +863,27 @@
   </si>
   <si>
     <t>Farinha Lactea</t>
+  </si>
+  <si>
+    <t>linha</t>
+  </si>
+  <si>
+    <t>produto</t>
+  </si>
+  <si>
+    <t>tamanho</t>
+  </si>
+  <si>
+    <t>ingredientes</t>
+  </si>
+  <si>
+    <t>modo de preparo</t>
+  </si>
+  <si>
+    <t>observacoes</t>
+  </si>
+  <si>
+    <t>imagem</t>
   </si>
 </sst>
 </file>
@@ -1237,4225 +1237,4225 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>281</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>282</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>283</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>284</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>285</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>286</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>287</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G3" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G4" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G5" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G6" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G7" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G8" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G9" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s">
         <v>14</v>
       </c>
-      <c r="D12" t="s">
-        <v>21</v>
-      </c>
       <c r="E12" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" t="s">
         <v>15</v>
       </c>
-      <c r="D13" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" t="s">
-        <v>22</v>
-      </c>
       <c r="G13" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E14" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G14" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D15" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E15" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G15" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E16" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G16" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D17" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E17" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G17" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D18" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E18" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G18" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D19" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E19" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G19" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C20" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D20" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E20" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G20" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E21" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G21" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B22" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D22" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E22" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G22" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D23" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E23" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G23" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D24" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E24" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G24" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D25" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E25" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G25" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B26" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D26" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E26" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="G26" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B27" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C27" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E27" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="G27" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C28" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E28" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="G28" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B29" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C29" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E29" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="G29" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B30" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D30" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E30" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="G30" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B31" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C31" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D31" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E31" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="G31" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C32" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D32" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E32" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="G32" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B33" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C33" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D33" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E33" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="G33" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D34" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E34" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G34" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C35" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D35" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E35" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G35" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C36" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D36" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E36" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G36" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B37" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C37" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D37" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E37" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G37" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D38" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E38" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G38" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C39" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D39" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E39" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G39" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B40" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C40" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D40" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E40" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G40" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B41" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C41" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D41" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E41" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G41" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B42" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C42" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D42" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E42" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="G42" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C43" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D43" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E43" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="G43" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B44" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C44" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D44" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E44" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="G44" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B45" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C45" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D45" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E45" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="G45" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D46" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E46" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="G46" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C47" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D47" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E47" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="G47" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B48" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C48" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D48" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E48" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="G48" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B49" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C49" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D49" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E49" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="G49" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B50" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C50" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D50" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E50" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="G50" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C51" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D51" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E51" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="G51" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B52" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C52" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D52" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E52" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="G52" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B53" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C53" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D53" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E53" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="G53" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B54" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C54" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D54" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E54" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G54" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B55" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C55" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D55" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E55" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G55" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B56" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C56" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D56" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E56" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G56" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B57" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C57" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D57" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E57" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G57" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B58" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C58" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F58" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G58" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B59" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C59" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B60" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C60" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B61" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C61" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B62" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C62" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F62" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G62" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B63" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C63" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B64" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C64" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B65" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C65" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B66" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C66" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B67" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C67" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B68" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C68" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B69" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C69" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B70" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="C70" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B71" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="C71" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B72" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="C72" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B73" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="C73" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B74" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C74" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B75" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C75" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B76" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C76" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B77" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C77" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B78" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C78" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F78" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G78" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B79" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C79" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B80" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C80" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B81" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C81" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B82" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B83" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="C83" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B84" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="C84" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B85" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="C85" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B86" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C86" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F86" t="s">
+        <v>64</v>
+      </c>
+      <c r="G86" t="s">
         <v>71</v>
-      </c>
-      <c r="G86" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B87" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C87" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B88" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C88" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B89" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C89" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B90" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="C90" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B91" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="C91" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B92" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="C92" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B93" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="C93" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B94" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C94" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F94" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="G94" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B95" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C95" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B96" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C96" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B97" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C97" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B98" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C98" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F98" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G98" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B99" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C99" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B100" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C100" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B101" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C101" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B102" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="C102" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B103" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="C103" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B104" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="C104" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B105" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="C105" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B106" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="C106" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B107" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="C107" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B108" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="C108" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B109" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="C109" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B110" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="C110" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B111" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="C111" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B112" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="C112" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B113" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="C113" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B114" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="C114" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="C115" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B116" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="C116" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="C117" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B118" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="C118" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B119" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="C119" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B120" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="C120" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B121" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="C121" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B122" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="C122" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B123" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="C123" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B124" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="C124" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B125" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="C125" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B126" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="C126" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B127" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="C127" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B128" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="C128" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B129" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="C129" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B130" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C130" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F130" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G130" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B131" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C131" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B132" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C132" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B133" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C133" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B134" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="C134" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B135" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="C135" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B136" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="C136" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B137" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="C137" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B138" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="C138" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B139" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="C139" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B140" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="C140" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B141" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="C141" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B142" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="C142" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B143" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="C143" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B144" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="C144" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B145" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="C145" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B146" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C146" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F146" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G146" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B147" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C147" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B148" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C148" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B149" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C149" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B150" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="C150" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B151" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="C151" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B152" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="C152" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B153" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="C153" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B154" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="C154" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B155" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="C155" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B156" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="C156" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B157" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="C157" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B158" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="C158" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B159" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="C159" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B160" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="C160" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B161" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="C161" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B162" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="C162" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B163" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="C163" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B164" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="C164" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B165" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="C165" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B166" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="C166" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B167" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="C167" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B168" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="C168" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B169" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="C169" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B170" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="C170" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B171" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="C171" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B172" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="C172" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B173" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="C173" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B174" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="C174" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B175" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="C175" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B176" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="C176" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B177" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="C177" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B178" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="C178" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B179" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="C179" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B180" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="C180" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B181" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="C181" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B182" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C182" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F182" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G182" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B183" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C183" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B184" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C184" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B185" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C185" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B186" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="C186" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B187" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="C187" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B188" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="C188" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B189" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="C189" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B190" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C190" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B191" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C191" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B192" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C192" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B193" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C193" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B194" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C194" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B195" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C195" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B196" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C196" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B197" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C197" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B198" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C198" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B199" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C199" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B200" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C200" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B201" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C201" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B202" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C202" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B203" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C203" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B204" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C204" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B205" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C205" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B206" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C206" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B207" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C207" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B208" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C208" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B209" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C209" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B210" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C210" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B211" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C211" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B212" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C212" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B213" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C213" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B214" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C214" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B215" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C215" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B216" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C216" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B217" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C217" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B218" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C218" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B219" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C219" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B220" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C220" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B221" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C221" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B222" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C222" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B223" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C223" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B224" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C224" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B225" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C225" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B226" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C226" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B227" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C227" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B228" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C228" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B229" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C229" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
+        <v>80</v>
+      </c>
+      <c r="B230" t="s">
+        <v>85</v>
+      </c>
+      <c r="C230" t="s">
+        <v>2</v>
+      </c>
+      <c r="D230" t="s">
+        <v>86</v>
+      </c>
+      <c r="E230" t="s">
         <v>87</v>
       </c>
-      <c r="B230" t="s">
-        <v>92</v>
-      </c>
-      <c r="C230" t="s">
-        <v>9</v>
-      </c>
-      <c r="D230" t="s">
-        <v>93</v>
-      </c>
-      <c r="E230" t="s">
-        <v>94</v>
-      </c>
       <c r="G230" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
+        <v>80</v>
+      </c>
+      <c r="B231" t="s">
+        <v>85</v>
+      </c>
+      <c r="C231" t="s">
+        <v>6</v>
+      </c>
+      <c r="D231" t="s">
+        <v>86</v>
+      </c>
+      <c r="E231" t="s">
         <v>87</v>
       </c>
-      <c r="B231" t="s">
-        <v>92</v>
-      </c>
-      <c r="C231" t="s">
-        <v>13</v>
-      </c>
-      <c r="D231" t="s">
-        <v>93</v>
-      </c>
-      <c r="E231" t="s">
-        <v>94</v>
-      </c>
       <c r="G231" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
+        <v>80</v>
+      </c>
+      <c r="B232" t="s">
+        <v>85</v>
+      </c>
+      <c r="C232" t="s">
+        <v>7</v>
+      </c>
+      <c r="D232" t="s">
+        <v>86</v>
+      </c>
+      <c r="E232" t="s">
         <v>87</v>
       </c>
-      <c r="B232" t="s">
-        <v>92</v>
-      </c>
-      <c r="C232" t="s">
-        <v>14</v>
-      </c>
-      <c r="D232" t="s">
-        <v>93</v>
-      </c>
-      <c r="E232" t="s">
-        <v>94</v>
-      </c>
       <c r="G232" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
+        <v>80</v>
+      </c>
+      <c r="B233" t="s">
+        <v>85</v>
+      </c>
+      <c r="C233" t="s">
+        <v>8</v>
+      </c>
+      <c r="D233" t="s">
+        <v>86</v>
+      </c>
+      <c r="E233" t="s">
         <v>87</v>
       </c>
-      <c r="B233" t="s">
-        <v>92</v>
-      </c>
-      <c r="C233" t="s">
-        <v>15</v>
-      </c>
-      <c r="D233" t="s">
-        <v>93</v>
-      </c>
-      <c r="E233" t="s">
-        <v>94</v>
-      </c>
       <c r="G233" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B234" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C234" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D234" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E234" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="G234" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B235" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C235" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D235" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E235" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="G235" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B236" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C236" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D236" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E236" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="G236" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B237" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C237" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D237" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E237" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="G237" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B238" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C238" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D238" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E238" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G238" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B239" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C239" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D239" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E239" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G239" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B240" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C240" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D240" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E240" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G240" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B241" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C241" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D241" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E241" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G241" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B242" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C242" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D242" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E242" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="G242" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B243" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C243" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D243" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E243" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="G243" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B244" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C244" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D244" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E244" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="G244" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B245" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C245" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D245" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E245" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="G245" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B246" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C246" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D246" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="E246" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="G246" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B247" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C247" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D247" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="E247" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="G247" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B248" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C248" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D248" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="E248" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="G248" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B249" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C249" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D249" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="E249" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="G249" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B250" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C250" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D250" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="E250" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="G250" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B251" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C251" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D251" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="E251" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="G251" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B252" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C252" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D252" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="E252" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="G252" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B253" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C253" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D253" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="E253" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="G253" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B254" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C254" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D254" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="E254" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="G254" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
+        <v>118</v>
+      </c>
+      <c r="B255" t="s">
+        <v>124</v>
+      </c>
+      <c r="C255" t="s">
+        <v>120</v>
+      </c>
+      <c r="D255" t="s">
         <v>125</v>
       </c>
-      <c r="B255" t="s">
-        <v>131</v>
-      </c>
-      <c r="C255" t="s">
+      <c r="E255" t="s">
+        <v>126</v>
+      </c>
+      <c r="G255" t="s">
         <v>127</v>
-      </c>
-      <c r="D255" t="s">
-        <v>132</v>
-      </c>
-      <c r="E255" t="s">
-        <v>133</v>
-      </c>
-      <c r="G255" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B256" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="C256" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D256" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="E256" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="G256" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B257" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C257" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D257" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E257" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="G257" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
+        <v>132</v>
+      </c>
+      <c r="B258" t="s">
+        <v>137</v>
+      </c>
+      <c r="C258" t="s">
+        <v>120</v>
+      </c>
+      <c r="D258" t="s">
+        <v>138</v>
+      </c>
+      <c r="E258" t="s">
         <v>139</v>
       </c>
-      <c r="B258" t="s">
-        <v>144</v>
-      </c>
-      <c r="C258" t="s">
-        <v>127</v>
-      </c>
-      <c r="D258" t="s">
-        <v>145</v>
-      </c>
-      <c r="E258" t="s">
-        <v>146</v>
-      </c>
       <c r="G258" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B259" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C259" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="F259" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="G259" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B260" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C260" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="F260" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="G260" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B261" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C261" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="F261" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="G261" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="B262" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C262" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D262" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="E262" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="G262" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
+        <v>147</v>
+      </c>
+      <c r="B263" t="s">
+        <v>152</v>
+      </c>
+      <c r="C263" t="s">
+        <v>120</v>
+      </c>
+      <c r="D263" t="s">
+        <v>153</v>
+      </c>
+      <c r="E263" t="s">
         <v>154</v>
       </c>
-      <c r="B263" t="s">
-        <v>159</v>
-      </c>
-      <c r="C263" t="s">
-        <v>127</v>
-      </c>
-      <c r="D263" t="s">
-        <v>160</v>
-      </c>
-      <c r="E263" t="s">
-        <v>161</v>
-      </c>
       <c r="G263" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="B264" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="C264" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D264" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="E264" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="G264" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="B265" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C265" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D265" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="E265" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="G265" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="B266" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="C266" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D266" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="E266" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="G266" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B267" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C267" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D267" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="E267" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="G267" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
+        <v>168</v>
+      </c>
+      <c r="B268" t="s">
+        <v>174</v>
+      </c>
+      <c r="C268" t="s">
+        <v>170</v>
+      </c>
+      <c r="D268" t="s">
         <v>175</v>
       </c>
-      <c r="B268" t="s">
-        <v>181</v>
-      </c>
-      <c r="C268" t="s">
+      <c r="E268" t="s">
+        <v>176</v>
+      </c>
+      <c r="G268" t="s">
         <v>177</v>
-      </c>
-      <c r="D268" t="s">
-        <v>182</v>
-      </c>
-      <c r="E268" t="s">
-        <v>183</v>
-      </c>
-      <c r="G268" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B269" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C269" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D269" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="E269" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="G269" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B270" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C270" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D270" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="E270" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="G270" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B271" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C271" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D271" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="E271" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="G271" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B272" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C272" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D272" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="E272" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="G272" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B273" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C273" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D273" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="E273" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="G273" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B274" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="C274" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D274" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="E274" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="G274" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B275" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C275" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D275" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="E275" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="G275" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B276" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C276" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D276" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="E276" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="G276" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B277" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="C277" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D277" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="E277" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="G277" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B278" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="C278" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D278" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="E278" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="G278" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B279" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="C279" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D279" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="E279" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="G279" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B280" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="C280" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D280" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="E280" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="G280" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B281" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="C281" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D281" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="E281" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="G281" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B282" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C282" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="D282" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="E282" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="G282" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B283" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C283" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D283" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="E283" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="G283" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B284" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="C284" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="D284" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="E284" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="G284" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="B285" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="C285" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="D285" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E285" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="F285" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="G285" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="B286" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C286" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="D286" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="E286" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="G286" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>

--- a/modelo_receitas_atualizado.xlsx
+++ b/modelo_receitas_atualizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\walte\Desktop\MilkShakeMix_Cardapio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{972E2437-9DF2-4263-B743-E71F1739D4CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2894FF75-6A06-4407-B1FD-3AC42230C319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="-45" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1217" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="289">
   <si>
     <t>Milkshakes Tradicionais</t>
   </si>
@@ -884,6 +884,9 @@
   </si>
   <si>
     <t>imagem</t>
+  </si>
+  <si>
+    <t>nutella.jpg</t>
   </si>
 </sst>
 </file>
@@ -3917,7 +3920,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>80</v>
       </c>
@@ -3928,7 +3931,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>80</v>
       </c>
@@ -3939,7 +3942,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>80</v>
       </c>
@@ -3950,7 +3953,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>80</v>
       </c>
@@ -3961,7 +3964,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>80</v>
       </c>
@@ -3972,7 +3975,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>80</v>
       </c>
@@ -3983,7 +3986,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>80</v>
       </c>
@@ -3994,7 +3997,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>80</v>
       </c>
@@ -4005,7 +4008,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>80</v>
       </c>
@@ -4016,7 +4019,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>80</v>
       </c>
@@ -4026,8 +4029,11 @@
       <c r="C202" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G202" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>80</v>
       </c>
@@ -4037,8 +4043,11 @@
       <c r="C203" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G203" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>80</v>
       </c>
@@ -4048,8 +4057,11 @@
       <c r="C204" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G204" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>80</v>
       </c>
@@ -4059,8 +4071,11 @@
       <c r="C205" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G205" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>80</v>
       </c>
@@ -4071,7 +4086,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>80</v>
       </c>
@@ -4082,7 +4097,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>80</v>
       </c>
